--- a/reductions/data/lit_dat.xlsx
+++ b/reductions/data/lit_dat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9501307F-9F26-4B03-AB60-8D834914C6F5}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD22B33B-D410-4439-BF3F-A8F66E503F89}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{DF353E34-80BC-440D-84E6-1A1BEACE8767}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{DF353E34-80BC-440D-84E6-1A1BEACE8767}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable explanation" sheetId="2" r:id="rId1"/>
@@ -301,7 +301,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9048" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9795" uniqueCount="1034">
   <si>
     <t>Study</t>
   </si>
@@ -3445,6 +3445,165 @@
   </si>
   <si>
     <t>DP.notes</t>
+  </si>
+  <si>
+    <t>Pedersen et al. 2021</t>
+  </si>
+  <si>
+    <t>Pedersen, J., T. Nyord, A. Feilberg, R. Labouriau, D. Hunt, S. Bittman. Effect of reduced exposed surface area and enhanced infiltration on ammonia emission from untreated and separated cattle slurry. doi.org/10.1016/j.biosystemseng.2021.09.003</t>
+  </si>
+  <si>
+    <t>Canada (Agassiz)</t>
+  </si>
+  <si>
+    <t>Temperate Oceanic</t>
+  </si>
+  <si>
+    <t>Kentucky bluegrass</t>
+  </si>
+  <si>
+    <t>wind tunnels</t>
+  </si>
+  <si>
+    <t>Separation</t>
+  </si>
+  <si>
+    <t>Narrow bands</t>
+  </si>
+  <si>
+    <t>wide bands</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Wagner et al. 2021</t>
+  </si>
+  <si>
+    <t>Wagner, C., T. Nyord, A.V. Vestergaard, S.D. Hafner, A.S. Pacholski. 2021. Acidification effects on in situ ammonia emissions and cereal yields depending on slurry type and application method. doi.org/10.3390/agriculture11111053</t>
+  </si>
+  <si>
+    <t>Barley</t>
+  </si>
+  <si>
+    <t>Incorporation</t>
+  </si>
+  <si>
+    <t>Band / incorporation</t>
+  </si>
+  <si>
+    <t>Acidified</t>
+  </si>
+  <si>
+    <t>trail hose</t>
+  </si>
+  <si>
+    <t>acidified</t>
+  </si>
+  <si>
+    <t>Anaerobic digestate</t>
+  </si>
+  <si>
+    <t>Wagner et al. 2022</t>
+  </si>
+  <si>
+    <t>Wagner, C., T. Nyord, A.V. Vestergaard, S.D. Hafner, A.S. Pacholski. 2021. Acidification effects on in situ ammonia emissions and cereal yields depending on slurry type and application method. doi.org/10.3390/agriculture11111054</t>
+  </si>
+  <si>
+    <t>Mink slurry</t>
+  </si>
+  <si>
+    <t>other slurry</t>
+  </si>
+  <si>
+    <t>Wagner et al. 2023</t>
+  </si>
+  <si>
+    <t>Wagner, C., T. Nyord, A.V. Vestergaard, S.D. Hafner, A.S. Pacholski. 2021. Acidification effects on in situ ammonia emissions and cereal yields depending on slurry type and application method. doi.org/10.3390/agriculture11111055</t>
+  </si>
+  <si>
+    <t>pig slurry</t>
+  </si>
+  <si>
+    <t>Wagner et al. 2024</t>
+  </si>
+  <si>
+    <t>Wagner, C., T. Nyord, A.V. Vestergaard, S.D. Hafner, A.S. Pacholski. 2021. Acidification effects on in situ ammonia emissions and cereal yields depending on slurry type and application method. doi.org/10.3390/agriculture11111056</t>
+  </si>
+  <si>
+    <t>liquid phase digestate</t>
+  </si>
+  <si>
+    <t>digested / separated / acid</t>
+  </si>
+  <si>
+    <t>Seidel et al., 2017</t>
+  </si>
+  <si>
+    <t>Seidel, A., A. Pacholski,T. Nyord, A. Vestergaard, I. Pahlmann, A. Herrmann, H. Kage. 2017. Effects of acidification and injection of pasture applied cattle slurry on ammonia losses, N2O emissions and crop N uptake. doi.org/10.1016/j.agee.2017.05.030</t>
+  </si>
+  <si>
+    <t>grassland</t>
+  </si>
+  <si>
+    <t>Injection (shallow)</t>
+  </si>
+  <si>
+    <t>Injection (deep)</t>
+  </si>
+  <si>
+    <t>acidified (light)</t>
+  </si>
+  <si>
+    <t>acidified (heavy)</t>
+  </si>
+  <si>
+    <t>Kai et al., 2008</t>
+  </si>
+  <si>
+    <t>Kai, P., P. Pedersen, J.E. Jensen, M.N. Hansen, S.G. Sommer. 2008. A whole-farm assessment of the efficacy of slurry acidification in reducing ammonia emissions. doi:10.1016/j.eja.2007.06.004</t>
+  </si>
+  <si>
+    <t>wheat</t>
+  </si>
+  <si>
+    <t>liquid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leunig </t>
+  </si>
+  <si>
+    <t>Andersson et al. 2023</t>
+  </si>
+  <si>
+    <t>Andersson, K., S. Delin, J. Pedersen, S.D. Hafner, T. Nyord. 2023. Ammonia emissions from untreated, separated and digested cattle slurry - Effects of slurry type and application strategy on a Swedish clay soil. doi.org/10.1016/j.biosystemseng.2023.01.012</t>
+  </si>
+  <si>
+    <t>temperate humid</t>
+  </si>
+  <si>
+    <t>Lanna field research station in south-west Sweden</t>
+  </si>
+  <si>
+    <t>grass ley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separated Dairy Slurry  </t>
+  </si>
+  <si>
+    <t>trailing hose</t>
+  </si>
+  <si>
+    <t>trailing shoe</t>
+  </si>
+  <si>
+    <t>digested</t>
+  </si>
+  <si>
+    <t>spring barley</t>
+  </si>
+  <si>
+    <t>Separated Cattle slurry</t>
   </si>
 </sst>
 </file>
@@ -3623,7 +3782,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3801,6 +3960,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4233,14 +4405,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7CE9C9-127E-4846-B34D-8BA0CB6E1A90}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="137.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="137.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4251,7 +4423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4262,7 +4434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4273,7 +4445,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4284,7 +4456,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4295,7 +4467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -4306,7 +4478,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -4317,7 +4489,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -4328,7 +4500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -4339,7 +4511,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -4350,7 +4522,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4361,7 +4533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4372,7 +4544,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4383,7 +4555,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -4394,7 +4566,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4405,7 +4577,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -4416,7 +4588,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -4427,7 +4599,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -4438,7 +4610,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -4449,7 +4621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -4460,7 +4632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -4471,7 +4643,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -4482,7 +4654,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -4493,7 +4665,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -4504,7 +4676,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -4515,7 +4687,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -4526,7 +4698,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -4537,7 +4709,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -4548,7 +4720,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -4559,7 +4731,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -4580,54 +4752,54 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D35D03E-84A5-4E70-9EFA-07826CEBC622}">
-  <dimension ref="A1:AY283"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AY320"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="1"/>
-    <col min="2" max="2" width="14.08984375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="59.90625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.90625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="6.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.453125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="19.36328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="14.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="59.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="2" customWidth="1"/>
+    <col min="9" max="10" width="19.42578125" style="2" customWidth="1"/>
     <col min="11" max="11" width="11" style="5" customWidth="1"/>
-    <col min="12" max="12" width="12.36328125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="5" customWidth="1"/>
     <col min="13" max="14" width="23" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.36328125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="11.08984375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.6328125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.6328125" style="2" customWidth="1"/>
-    <col min="27" max="28" width="9.453125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="20.453125" style="2" customWidth="1"/>
-    <col min="30" max="31" width="44.6328125" style="1" customWidth="1"/>
-    <col min="32" max="33" width="18.453125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="11.140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.5703125" style="2" customWidth="1"/>
+    <col min="27" max="28" width="9.42578125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="20.42578125" style="2" customWidth="1"/>
+    <col min="30" max="31" width="44.5703125" style="1" customWidth="1"/>
+    <col min="32" max="33" width="18.42578125" style="2" customWidth="1"/>
     <col min="34" max="36" width="19" style="2" customWidth="1"/>
-    <col min="37" max="37" width="8.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="15" style="1" customWidth="1"/>
-    <col min="41" max="41" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="17" style="1" customWidth="1"/>
-    <col min="44" max="44" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="6.54296875" style="2" customWidth="1"/>
-    <col min="48" max="48" width="6.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="6.6328125" style="2" customWidth="1"/>
-    <col min="50" max="50" width="10.453125" style="1" customWidth="1"/>
-    <col min="51" max="51" width="27.6328125" style="1" customWidth="1"/>
-    <col min="52" max="52" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="16384" width="8.90625" style="1"/>
+    <col min="44" max="44" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="6.5703125" style="2" customWidth="1"/>
+    <col min="48" max="48" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="6.5703125" style="2" customWidth="1"/>
+    <col min="50" max="50" width="10.42578125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="27.5703125" style="1" customWidth="1"/>
+    <col min="52" max="52" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:51" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>974</v>
       </c>
@@ -4782,7 +4954,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4930,7 +5102,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -5080,7 +5252,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -5224,7 +5396,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5374,7 +5546,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5516,7 +5688,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5663,7 +5835,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5805,7 +5977,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5952,7 +6124,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6094,7 +6266,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6241,7 +6413,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6383,7 +6555,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -6531,7 +6703,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>2</v>
       </c>
@@ -6676,7 +6848,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -6814,7 +6986,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="16" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>3</v>
       </c>
@@ -6952,7 +7124,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>5</v>
       </c>
@@ -7087,7 +7259,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="18" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>7</v>
       </c>
@@ -7226,7 +7398,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -7365,7 +7537,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>8</v>
       </c>
@@ -7501,7 +7673,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>8</v>
       </c>
@@ -7640,7 +7812,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>8</v>
       </c>
@@ -7776,7 +7948,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>8</v>
       </c>
@@ -7912,7 +8084,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>8</v>
       </c>
@@ -8048,7 +8220,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>8</v>
       </c>
@@ -8183,7 +8355,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>8</v>
       </c>
@@ -8318,7 +8490,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>8</v>
       </c>
@@ -8454,7 +8626,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>8</v>
       </c>
@@ -8590,7 +8762,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="29" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>9</v>
       </c>
@@ -8730,7 +8902,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="30" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>9</v>
       </c>
@@ -8870,7 +9042,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="31" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>9</v>
       </c>
@@ -9011,7 +9183,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="32" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>10</v>
       </c>
@@ -9148,7 +9320,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="33" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>10</v>
       </c>
@@ -9289,7 +9461,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>14</v>
       </c>
@@ -9427,7 +9599,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>14</v>
       </c>
@@ -9565,7 +9737,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>14</v>
       </c>
@@ -9709,7 +9881,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>14</v>
       </c>
@@ -9853,7 +10025,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>14</v>
       </c>
@@ -9997,7 +10169,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>14</v>
       </c>
@@ -10143,7 +10315,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>16</v>
       </c>
@@ -10285,7 +10457,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>16</v>
       </c>
@@ -10429,7 +10601,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>16</v>
       </c>
@@ -10574,7 +10746,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>17</v>
       </c>
@@ -10656,7 +10828,7 @@
         <v>2.4390243902439024</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>17</v>
       </c>
@@ -10738,7 +10910,7 @@
         <v>7.3170731707317076</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>17</v>
       </c>
@@ -10820,7 +10992,7 @@
         <v>7.3170731707317076</v>
       </c>
     </row>
-    <row r="46" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>17</v>
       </c>
@@ -10910,7 +11082,7 @@
       </c>
       <c r="AW46" s="11"/>
     </row>
-    <row r="47" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>18</v>
       </c>
@@ -11042,7 +11214,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="48" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>18</v>
       </c>
@@ -11179,7 +11351,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>20</v>
       </c>
@@ -11321,7 +11493,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>20</v>
       </c>
@@ -11460,7 +11632,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>20</v>
       </c>
@@ -11599,7 +11771,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="52" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>20</v>
       </c>
@@ -11738,7 +11910,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>20</v>
       </c>
@@ -11877,7 +12049,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:50" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>20</v>
       </c>
@@ -12019,7 +12191,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>20</v>
       </c>
@@ -12158,7 +12330,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>20</v>
       </c>
@@ -12297,7 +12469,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>20</v>
       </c>
@@ -12436,7 +12608,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="58" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>20</v>
       </c>
@@ -12576,7 +12748,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="59" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>21</v>
       </c>
@@ -12720,7 +12892,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>21</v>
       </c>
@@ -12864,7 +13036,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>22</v>
       </c>
@@ -13001,7 +13173,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>22</v>
       </c>
@@ -13138,7 +13310,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>22</v>
       </c>
@@ -13273,7 +13445,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="64" spans="1:50" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>22</v>
       </c>
@@ -13411,7 +13583,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="65" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>22</v>
       </c>
@@ -13546,7 +13718,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="66" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>22</v>
       </c>
@@ -13681,7 +13853,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="67" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>22</v>
       </c>
@@ -13816,7 +13988,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="68" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>22</v>
       </c>
@@ -13951,7 +14123,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="69" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>22</v>
       </c>
@@ -14086,7 +14258,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="70" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>22</v>
       </c>
@@ -14224,7 +14396,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="71" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>23</v>
       </c>
@@ -14363,7 +14535,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="72" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>23</v>
       </c>
@@ -14505,7 +14677,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="73" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>25</v>
       </c>
@@ -14648,7 +14820,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="74" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>25</v>
       </c>
@@ -14791,7 +14963,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="75" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>25</v>
       </c>
@@ -14935,7 +15107,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="76" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>26</v>
       </c>
@@ -15072,7 +15244,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="77" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>27</v>
       </c>
@@ -15209,7 +15381,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="78" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>27</v>
       </c>
@@ -15346,7 +15518,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="79" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>27</v>
       </c>
@@ -15483,7 +15655,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="80" spans="1:49" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:49" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="22">
         <v>27</v>
       </c>
@@ -15623,7 +15795,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>27</v>
       </c>
@@ -15760,7 +15932,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="82" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>27</v>
       </c>
@@ -15897,7 +16069,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="83" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>27</v>
       </c>
@@ -16034,7 +16206,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="84" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>27</v>
       </c>
@@ -16174,7 +16346,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>28</v>
       </c>
@@ -16320,7 +16492,7 @@
         <v>8.3333333333333321</v>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>28</v>
       </c>
@@ -16466,7 +16638,7 @@
         <v>58.63636363636364</v>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>28</v>
       </c>
@@ -16612,7 +16784,7 @@
         <v>11.363636363636363</v>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>28</v>
       </c>
@@ -16759,7 +16931,7 @@
         <v>36.679536679536682</v>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>28</v>
       </c>
@@ -16906,7 +17078,7 @@
         <v>6.5512517125420446</v>
       </c>
     </row>
-    <row r="90" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>28</v>
       </c>
@@ -17052,7 +17224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>28</v>
       </c>
@@ -17199,7 +17371,7 @@
         <v>34.234234234234236</v>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>28</v>
       </c>
@@ -17346,7 +17518,7 @@
         <v>62.166891300749562</v>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>28</v>
       </c>
@@ -17493,7 +17665,7 @@
         <v>9.9099099099099011</v>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>28</v>
       </c>
@@ -17640,7 +17812,7 @@
         <v>23.273657289002564</v>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>28</v>
       </c>
@@ -17787,7 +17959,7 @@
         <v>71.803069053708441</v>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>28</v>
       </c>
@@ -17934,7 +18106,7 @@
         <v>42.455242966751925</v>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>28</v>
       </c>
@@ -18081,7 +18253,7 @@
         <v>28.169014084507033</v>
       </c>
     </row>
-    <row r="98" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>28</v>
       </c>
@@ -18228,7 +18400,7 @@
         <v>64.967989756722162</v>
       </c>
     </row>
-    <row r="99" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>28</v>
       </c>
@@ -18375,7 +18547,7 @@
         <v>7.0422535211267583</v>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>28</v>
       </c>
@@ -18522,7 +18694,7 @@
         <v>39.344262295081968</v>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>28</v>
       </c>
@@ -18669,7 +18841,7 @@
         <v>60.000000000000007</v>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>28</v>
       </c>
@@ -18816,7 +18988,7 @@
         <v>60.655737704918032</v>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>28</v>
       </c>
@@ -18963,7 +19135,7 @@
         <v>30.705394190871377</v>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>28</v>
       </c>
@@ -19110,7 +19282,7 @@
         <v>48.091286307053934</v>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>28</v>
       </c>
@@ -19257,7 +19429,7 @@
         <v>32.780082987551864</v>
       </c>
     </row>
-    <row r="106" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>28</v>
       </c>
@@ -19404,7 +19576,7 @@
         <v>-26.842105263157919</v>
       </c>
     </row>
-    <row r="107" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>28</v>
       </c>
@@ -19551,7 +19723,7 @@
         <v>-7.1889952153110155</v>
       </c>
     </row>
-    <row r="108" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>28</v>
       </c>
@@ -19700,7 +19872,7 @@
         <v>-46.842105263157904</v>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>29</v>
       </c>
@@ -19845,7 +20017,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>29</v>
       </c>
@@ -19990,7 +20162,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>29</v>
       </c>
@@ -20135,7 +20307,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="112" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>29</v>
       </c>
@@ -20280,7 +20452,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="113" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>29</v>
       </c>
@@ -20426,7 +20598,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="114" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>31</v>
       </c>
@@ -20565,7 +20737,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="115" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>31</v>
       </c>
@@ -20704,7 +20876,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="116" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>31</v>
       </c>
@@ -20843,7 +21015,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="117" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>31</v>
       </c>
@@ -20982,7 +21154,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="118" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>31</v>
       </c>
@@ -21123,7 +21295,7 @@
       <c r="AX118" s="1"/>
       <c r="AY118" s="1"/>
     </row>
-    <row r="119" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>31</v>
       </c>
@@ -21264,7 +21436,7 @@
       <c r="AX119" s="8"/>
       <c r="AY119" s="8"/>
     </row>
-    <row r="120" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>32</v>
       </c>
@@ -21407,7 +21579,7 @@
       </c>
       <c r="AY120" s="1"/>
     </row>
-    <row r="121" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>32</v>
       </c>
@@ -21550,7 +21722,7 @@
       </c>
       <c r="AY121" s="1"/>
     </row>
-    <row r="122" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>32</v>
       </c>
@@ -21693,7 +21865,7 @@
       </c>
       <c r="AY122" s="1"/>
     </row>
-    <row r="123" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>32</v>
       </c>
@@ -21836,7 +22008,7 @@
       </c>
       <c r="AY123" s="1"/>
     </row>
-    <row r="124" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>32</v>
       </c>
@@ -21977,7 +22149,7 @@
       <c r="AX124" s="1"/>
       <c r="AY124" s="1"/>
     </row>
-    <row r="125" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>32</v>
       </c>
@@ -22120,7 +22292,7 @@
       </c>
       <c r="AY125" s="1"/>
     </row>
-    <row r="126" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>32</v>
       </c>
@@ -22263,7 +22435,7 @@
       </c>
       <c r="AY126" s="1"/>
     </row>
-    <row r="127" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>32</v>
       </c>
@@ -22406,7 +22578,7 @@
       </c>
       <c r="AY127" s="1"/>
     </row>
-    <row r="128" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>32</v>
       </c>
@@ -22547,7 +22719,7 @@
       <c r="AX128" s="1"/>
       <c r="AY128" s="1"/>
     </row>
-    <row r="129" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>32</v>
       </c>
@@ -22688,7 +22860,7 @@
       <c r="AX129" s="1"/>
       <c r="AY129" s="1"/>
     </row>
-    <row r="130" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>32</v>
       </c>
@@ -22829,7 +23001,7 @@
       <c r="AX130" s="1"/>
       <c r="AY130" s="36"/>
     </row>
-    <row r="131" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>32</v>
       </c>
@@ -22970,7 +23142,7 @@
       <c r="AX131" s="1"/>
       <c r="AY131" s="36"/>
     </row>
-    <row r="132" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>32</v>
       </c>
@@ -23111,7 +23283,7 @@
       <c r="AX132" s="8"/>
       <c r="AY132" s="36"/>
     </row>
-    <row r="133" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>34</v>
       </c>
@@ -23260,7 +23432,7 @@
       <c r="AX133" s="1"/>
       <c r="AY133" s="3"/>
     </row>
-    <row r="134" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>34</v>
       </c>
@@ -23409,7 +23581,7 @@
       <c r="AX134" s="1"/>
       <c r="AY134" s="1"/>
     </row>
-    <row r="135" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>34</v>
       </c>
@@ -23559,7 +23731,7 @@
       <c r="AX135" s="1"/>
       <c r="AY135" s="1"/>
     </row>
-    <row r="136" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>34</v>
       </c>
@@ -23709,7 +23881,7 @@
       <c r="AX136" s="1"/>
       <c r="AY136" s="1"/>
     </row>
-    <row r="137" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>35</v>
       </c>
@@ -23850,7 +24022,7 @@
       <c r="AX137" s="1"/>
       <c r="AY137" s="1"/>
     </row>
-    <row r="138" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>35</v>
       </c>
@@ -23991,7 +24163,7 @@
       <c r="AX138" s="1"/>
       <c r="AY138" s="1"/>
     </row>
-    <row r="139" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>35</v>
       </c>
@@ -24132,7 +24304,7 @@
       <c r="AX139" s="1"/>
       <c r="AY139" s="1"/>
     </row>
-    <row r="140" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>35</v>
       </c>
@@ -24273,7 +24445,7 @@
       <c r="AX140" s="1"/>
       <c r="AY140" s="1"/>
     </row>
-    <row r="141" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>35</v>
       </c>
@@ -24414,7 +24586,7 @@
       <c r="AX141" s="1"/>
       <c r="AY141" s="1"/>
     </row>
-    <row r="142" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>35</v>
       </c>
@@ -24555,7 +24727,7 @@
       <c r="AX142" s="1"/>
       <c r="AY142" s="1"/>
     </row>
-    <row r="143" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>35</v>
       </c>
@@ -24696,7 +24868,7 @@
       <c r="AX143" s="1"/>
       <c r="AY143" s="1"/>
     </row>
-    <row r="144" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>35</v>
       </c>
@@ -24837,7 +25009,7 @@
       <c r="AX144" s="8"/>
       <c r="AY144" s="8"/>
     </row>
-    <row r="145" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>36</v>
       </c>
@@ -24978,7 +25150,7 @@
       <c r="AX145" s="36"/>
       <c r="AY145" s="1"/>
     </row>
-    <row r="146" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>36</v>
       </c>
@@ -25119,7 +25291,7 @@
       <c r="AX146" s="36"/>
       <c r="AY146" s="1"/>
     </row>
-    <row r="147" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>36</v>
       </c>
@@ -25260,7 +25432,7 @@
       <c r="AX147" s="36"/>
       <c r="AY147" s="1"/>
     </row>
-    <row r="148" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>36</v>
       </c>
@@ -25401,7 +25573,7 @@
       <c r="AX148" s="36"/>
       <c r="AY148" s="1"/>
     </row>
-    <row r="149" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>36</v>
       </c>
@@ -25542,7 +25714,7 @@
       <c r="AX149" s="36"/>
       <c r="AY149" s="1"/>
     </row>
-    <row r="150" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>36</v>
       </c>
@@ -25683,7 +25855,7 @@
       <c r="AX150" s="36"/>
       <c r="AY150" s="1"/>
     </row>
-    <row r="151" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>36</v>
       </c>
@@ -25824,7 +25996,7 @@
       <c r="AX151" s="36"/>
       <c r="AY151" s="1"/>
     </row>
-    <row r="152" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>36</v>
       </c>
@@ -25965,7 +26137,7 @@
       <c r="AX152" s="36"/>
       <c r="AY152" s="1"/>
     </row>
-    <row r="153" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>36</v>
       </c>
@@ -26106,7 +26278,7 @@
       <c r="AX153" s="36"/>
       <c r="AY153" s="1"/>
     </row>
-    <row r="154" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>36</v>
       </c>
@@ -26247,7 +26419,7 @@
       <c r="AX154" s="36"/>
       <c r="AY154" s="1"/>
     </row>
-    <row r="155" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>36</v>
       </c>
@@ -26388,7 +26560,7 @@
       <c r="AX155" s="36"/>
       <c r="AY155" s="1"/>
     </row>
-    <row r="156" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>36</v>
       </c>
@@ -26529,7 +26701,7 @@
       <c r="AX156" s="36"/>
       <c r="AY156" s="1"/>
     </row>
-    <row r="157" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>36</v>
       </c>
@@ -26670,7 +26842,7 @@
       <c r="AX157" s="36"/>
       <c r="AY157" s="1"/>
     </row>
-    <row r="158" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>36</v>
       </c>
@@ -26811,7 +26983,7 @@
       <c r="AX158" s="36"/>
       <c r="AY158" s="1"/>
     </row>
-    <row r="159" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>36</v>
       </c>
@@ -26952,7 +27124,7 @@
       <c r="AX159" s="36"/>
       <c r="AY159" s="1"/>
     </row>
-    <row r="160" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>36</v>
       </c>
@@ -27093,7 +27265,7 @@
       <c r="AX160" s="37"/>
       <c r="AY160" s="8"/>
     </row>
-    <row r="161" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>37</v>
       </c>
@@ -27233,7 +27405,7 @@
       <c r="AX161" s="1"/>
       <c r="AY161" s="1"/>
     </row>
-    <row r="162" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>38</v>
       </c>
@@ -27383,7 +27555,7 @@
       </c>
       <c r="AY162" s="1"/>
     </row>
-    <row r="163" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>38</v>
       </c>
@@ -27531,7 +27703,7 @@
       <c r="AX163" s="1"/>
       <c r="AY163" s="1"/>
     </row>
-    <row r="164" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>38</v>
       </c>
@@ -27679,7 +27851,7 @@
       <c r="AX164" s="1"/>
       <c r="AY164" s="1"/>
     </row>
-    <row r="165" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>38</v>
       </c>
@@ -27827,7 +27999,7 @@
       <c r="AX165" s="8"/>
       <c r="AY165" s="8"/>
     </row>
-    <row r="166" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>39</v>
       </c>
@@ -27970,7 +28142,7 @@
       </c>
       <c r="AY166" s="1"/>
     </row>
-    <row r="167" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>39</v>
       </c>
@@ -28111,7 +28283,7 @@
       <c r="AX167" s="1"/>
       <c r="AY167" s="1"/>
     </row>
-    <row r="168" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>39</v>
       </c>
@@ -28252,7 +28424,7 @@
       <c r="AX168" s="1"/>
       <c r="AY168" s="1"/>
     </row>
-    <row r="169" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>39</v>
       </c>
@@ -28393,7 +28565,7 @@
       <c r="AX169" s="1"/>
       <c r="AY169" s="1"/>
     </row>
-    <row r="170" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>39</v>
       </c>
@@ -28534,7 +28706,7 @@
       <c r="AX170" s="1"/>
       <c r="AY170" s="1"/>
     </row>
-    <row r="171" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>39</v>
       </c>
@@ -28675,7 +28847,7 @@
       <c r="AX171" s="1"/>
       <c r="AY171" s="1"/>
     </row>
-    <row r="172" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>39</v>
       </c>
@@ -28816,7 +28988,7 @@
       <c r="AX172" s="1"/>
       <c r="AY172" s="1"/>
     </row>
-    <row r="173" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>39</v>
       </c>
@@ -28957,7 +29129,7 @@
       <c r="AX173" s="8"/>
       <c r="AY173" s="8"/>
     </row>
-    <row r="174" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>40</v>
       </c>
@@ -29104,7 +29276,7 @@
       </c>
       <c r="AY174" s="8"/>
     </row>
-    <row r="175" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>41</v>
       </c>
@@ -29241,7 +29413,7 @@
       </c>
       <c r="AY175" s="1"/>
     </row>
-    <row r="176" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>41</v>
       </c>
@@ -29375,7 +29547,7 @@
       </c>
       <c r="AY176" s="1"/>
     </row>
-    <row r="177" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>41</v>
       </c>
@@ -29510,7 +29682,7 @@
       <c r="AX177" s="1"/>
       <c r="AY177" s="1"/>
     </row>
-    <row r="178" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>41</v>
       </c>
@@ -29645,7 +29817,7 @@
       <c r="AX178" s="1"/>
       <c r="AY178" s="1"/>
     </row>
-    <row r="179" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>41</v>
       </c>
@@ -29780,7 +29952,7 @@
       <c r="AX179" s="1"/>
       <c r="AY179" s="1"/>
     </row>
-    <row r="180" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>41</v>
       </c>
@@ -29915,7 +30087,7 @@
       <c r="AX180" s="1"/>
       <c r="AY180" s="1"/>
     </row>
-    <row r="181" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>41</v>
       </c>
@@ -30050,7 +30222,7 @@
       <c r="AX181" s="1"/>
       <c r="AY181" s="1"/>
     </row>
-    <row r="182" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>42</v>
       </c>
@@ -30197,7 +30369,7 @@
       </c>
       <c r="AY182" s="1"/>
     </row>
-    <row r="183" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>42</v>
       </c>
@@ -30342,7 +30514,7 @@
       <c r="AX183" s="8"/>
       <c r="AY183" s="8"/>
     </row>
-    <row r="184" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>43</v>
       </c>
@@ -30482,7 +30654,7 @@
       <c r="AX184" s="1"/>
       <c r="AY184" s="1"/>
     </row>
-    <row r="185" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>43</v>
       </c>
@@ -30622,7 +30794,7 @@
       <c r="AX185" s="1"/>
       <c r="AY185" s="1"/>
     </row>
-    <row r="186" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>43</v>
       </c>
@@ -30762,7 +30934,7 @@
       <c r="AX186" s="1"/>
       <c r="AY186" s="1"/>
     </row>
-    <row r="187" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>44</v>
       </c>
@@ -30902,7 +31074,7 @@
       <c r="AX187" s="1"/>
       <c r="AY187" s="1"/>
     </row>
-    <row r="188" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>44</v>
       </c>
@@ -31042,7 +31214,7 @@
       <c r="AX188" s="1"/>
       <c r="AY188" s="1"/>
     </row>
-    <row r="189" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>44</v>
       </c>
@@ -31182,7 +31354,7 @@
       <c r="AX189" s="1"/>
       <c r="AY189" s="1"/>
     </row>
-    <row r="190" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>44</v>
       </c>
@@ -31322,7 +31494,7 @@
       <c r="AX190" s="1"/>
       <c r="AY190" s="1"/>
     </row>
-    <row r="191" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>44</v>
       </c>
@@ -31463,7 +31635,7 @@
       <c r="AX191" s="1"/>
       <c r="AY191" s="1"/>
     </row>
-    <row r="192" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>44</v>
       </c>
@@ -31604,7 +31776,7 @@
       <c r="AX192" s="1"/>
       <c r="AY192" s="1"/>
     </row>
-    <row r="193" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>44</v>
       </c>
@@ -31745,7 +31917,7 @@
       <c r="AX193" s="1"/>
       <c r="AY193" s="1"/>
     </row>
-    <row r="194" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>45</v>
       </c>
@@ -31888,7 +32060,7 @@
       </c>
       <c r="AY194" s="1"/>
     </row>
-    <row r="195" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>45</v>
       </c>
@@ -32029,7 +32201,7 @@
       <c r="AX195" s="1"/>
       <c r="AY195" s="1"/>
     </row>
-    <row r="196" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>45</v>
       </c>
@@ -32170,7 +32342,7 @@
       <c r="AX196" s="1"/>
       <c r="AY196" s="1"/>
     </row>
-    <row r="197" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>45</v>
       </c>
@@ -32311,7 +32483,7 @@
       <c r="AX197" s="1"/>
       <c r="AY197" s="1"/>
     </row>
-    <row r="198" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>45</v>
       </c>
@@ -32452,7 +32624,7 @@
       <c r="AX198" s="1"/>
       <c r="AY198" s="1"/>
     </row>
-    <row r="199" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>45</v>
       </c>
@@ -32593,7 +32765,7 @@
       <c r="AX199" s="1"/>
       <c r="AY199" s="1"/>
     </row>
-    <row r="200" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>45</v>
       </c>
@@ -32734,7 +32906,7 @@
       <c r="AX200" s="1"/>
       <c r="AY200" s="1"/>
     </row>
-    <row r="201" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>45</v>
       </c>
@@ -32875,7 +33047,7 @@
       <c r="AX201" s="1"/>
       <c r="AY201" s="1"/>
     </row>
-    <row r="202" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46</v>
       </c>
@@ -33021,7 +33193,7 @@
       </c>
       <c r="AY202" s="8"/>
     </row>
-    <row r="203" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>46</v>
       </c>
@@ -33164,7 +33336,7 @@
       </c>
       <c r="AY203" s="1"/>
     </row>
-    <row r="204" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>46</v>
       </c>
@@ -33305,7 +33477,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="205" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>46</v>
       </c>
@@ -33444,7 +33616,7 @@
       <c r="AX205" s="1"/>
       <c r="AY205" s="3"/>
     </row>
-    <row r="206" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>46</v>
       </c>
@@ -33583,7 +33755,7 @@
       <c r="AX206" s="1"/>
       <c r="AY206" s="3"/>
     </row>
-    <row r="207" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>47</v>
       </c>
@@ -33724,7 +33896,7 @@
       <c r="AX207" s="1"/>
       <c r="AY207" s="1"/>
     </row>
-    <row r="208" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>47</v>
       </c>
@@ -33865,7 +34037,7 @@
       <c r="AX208" s="1"/>
       <c r="AY208" s="1"/>
     </row>
-    <row r="209" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="8">
         <v>47</v>
       </c>
@@ -34006,7 +34178,7 @@
       <c r="AX209" s="8"/>
       <c r="AY209" s="8"/>
     </row>
-    <row r="210" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>48</v>
       </c>
@@ -34155,7 +34327,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="211" spans="1:51" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:51" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="22">
         <v>48</v>
       </c>
@@ -34303,7 +34475,7 @@
       <c r="AX211" s="22"/>
       <c r="AY211" s="22"/>
     </row>
-    <row r="212" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>48</v>
       </c>
@@ -34450,7 +34622,7 @@
       <c r="AX212" s="1"/>
       <c r="AY212" s="1"/>
     </row>
-    <row r="213" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="8">
         <v>48</v>
       </c>
@@ -34599,7 +34771,7 @@
       </c>
       <c r="AY213" s="8"/>
     </row>
-    <row r="214" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>49</v>
       </c>
@@ -34748,7 +34920,7 @@
       <c r="AX214" s="1"/>
       <c r="AY214" s="1"/>
     </row>
-    <row r="215" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>49</v>
       </c>
@@ -34897,7 +35069,7 @@
       <c r="AX215" s="1"/>
       <c r="AY215" s="1"/>
     </row>
-    <row r="216" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>49</v>
       </c>
@@ -35046,7 +35218,7 @@
       <c r="AX216" s="8"/>
       <c r="AY216" s="8"/>
     </row>
-    <row r="217" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>50</v>
       </c>
@@ -35189,7 +35361,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="218" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>50</v>
       </c>
@@ -35330,7 +35502,7 @@
       <c r="AX218" s="1"/>
       <c r="AY218" s="1"/>
     </row>
-    <row r="219" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>50</v>
       </c>
@@ -35471,7 +35643,7 @@
       <c r="AX219" s="1"/>
       <c r="AY219" s="1"/>
     </row>
-    <row r="220" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>50</v>
       </c>
@@ -35613,7 +35785,7 @@
       <c r="AX220" s="1"/>
       <c r="AY220" s="1"/>
     </row>
-    <row r="221" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>50</v>
       </c>
@@ -35755,7 +35927,7 @@
       <c r="AX221" s="1"/>
       <c r="AY221" s="1"/>
     </row>
-    <row r="222" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>50</v>
       </c>
@@ -35897,7 +36069,7 @@
       <c r="AX222" s="1"/>
       <c r="AY222" s="1"/>
     </row>
-    <row r="223" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>50</v>
       </c>
@@ -36039,7 +36211,7 @@
       <c r="AX223" s="1"/>
       <c r="AY223" s="1"/>
     </row>
-    <row r="224" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>50</v>
       </c>
@@ -36181,7 +36353,7 @@
       <c r="AX224" s="1"/>
       <c r="AY224" s="1"/>
     </row>
-    <row r="225" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>51</v>
       </c>
@@ -36329,7 +36501,7 @@
       </c>
       <c r="AY225" s="1"/>
     </row>
-    <row r="226" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>51</v>
       </c>
@@ -36477,7 +36649,7 @@
       </c>
       <c r="AY226" s="1"/>
     </row>
-    <row r="227" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>51</v>
       </c>
@@ -36625,7 +36797,7 @@
       </c>
       <c r="AY227" s="1"/>
     </row>
-    <row r="228" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>51</v>
       </c>
@@ -36773,7 +36945,7 @@
       </c>
       <c r="AY228" s="1"/>
     </row>
-    <row r="229" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>51</v>
       </c>
@@ -36921,7 +37093,7 @@
       </c>
       <c r="AY229" s="1"/>
     </row>
-    <row r="230" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>51</v>
       </c>
@@ -37070,7 +37242,7 @@
       </c>
       <c r="AY230" s="1"/>
     </row>
-    <row r="231" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>51</v>
       </c>
@@ -37220,7 +37392,7 @@
       </c>
       <c r="AY231" s="1"/>
     </row>
-    <row r="232" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>51</v>
       </c>
@@ -37370,7 +37542,7 @@
       </c>
       <c r="AY232" s="1"/>
     </row>
-    <row r="233" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>51</v>
       </c>
@@ -37520,7 +37692,7 @@
       </c>
       <c r="AY233" s="1"/>
     </row>
-    <row r="234" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>51</v>
       </c>
@@ -37671,7 +37843,7 @@
       </c>
       <c r="AY234" s="1"/>
     </row>
-    <row r="235" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>51</v>
       </c>
@@ -37822,7 +37994,7 @@
       </c>
       <c r="AY235" s="1"/>
     </row>
-    <row r="236" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>51</v>
       </c>
@@ -37973,7 +38145,7 @@
       </c>
       <c r="AY236" s="1"/>
     </row>
-    <row r="237" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>51</v>
       </c>
@@ -38122,7 +38294,7 @@
       </c>
       <c r="AY237" s="1"/>
     </row>
-    <row r="238" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>51</v>
       </c>
@@ -38271,7 +38443,7 @@
       </c>
       <c r="AY238" s="1"/>
     </row>
-    <row r="239" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>51</v>
       </c>
@@ -38420,7 +38592,7 @@
       </c>
       <c r="AY239" s="1"/>
     </row>
-    <row r="240" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>51</v>
       </c>
@@ -38569,7 +38741,7 @@
       </c>
       <c r="AY240" s="1"/>
     </row>
-    <row r="241" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>51</v>
       </c>
@@ -38718,7 +38890,7 @@
       </c>
       <c r="AY241" s="1"/>
     </row>
-    <row r="242" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>51</v>
       </c>
@@ -38867,7 +39039,7 @@
       </c>
       <c r="AY242" s="1"/>
     </row>
-    <row r="243" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>51</v>
       </c>
@@ -39016,7 +39188,7 @@
       </c>
       <c r="AY243" s="1"/>
     </row>
-    <row r="244" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>51</v>
       </c>
@@ -39166,7 +39338,7 @@
       </c>
       <c r="AY244" s="1"/>
     </row>
-    <row r="245" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>51</v>
       </c>
@@ -39316,7 +39488,7 @@
       </c>
       <c r="AY245" s="1"/>
     </row>
-    <row r="246" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>51</v>
       </c>
@@ -39465,7 +39637,7 @@
       </c>
       <c r="AY246" s="1"/>
     </row>
-    <row r="247" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>51</v>
       </c>
@@ -39615,7 +39787,7 @@
       </c>
       <c r="AY247" s="1"/>
     </row>
-    <row r="248" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>51</v>
       </c>
@@ -39765,7 +39937,7 @@
       </c>
       <c r="AY248" s="1"/>
     </row>
-    <row r="249" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>51</v>
       </c>
@@ -39913,7 +40085,7 @@
       </c>
       <c r="AY249" s="1"/>
     </row>
-    <row r="250" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>51</v>
       </c>
@@ -40062,7 +40234,7 @@
       </c>
       <c r="AY250" s="1"/>
     </row>
-    <row r="251" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>51</v>
       </c>
@@ -40210,7 +40382,7 @@
       </c>
       <c r="AY251" s="1"/>
     </row>
-    <row r="252" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>51</v>
       </c>
@@ -40359,7 +40531,7 @@
       </c>
       <c r="AY252" s="1"/>
     </row>
-    <row r="253" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>51</v>
       </c>
@@ -40508,7 +40680,7 @@
       </c>
       <c r="AY253" s="1"/>
     </row>
-    <row r="254" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>51</v>
       </c>
@@ -40658,7 +40830,7 @@
       </c>
       <c r="AY254" s="1"/>
     </row>
-    <row r="255" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>51</v>
       </c>
@@ -40807,7 +40979,7 @@
       </c>
       <c r="AY255" s="1"/>
     </row>
-    <row r="256" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>51</v>
       </c>
@@ -40957,7 +41129,7 @@
       </c>
       <c r="AY256" s="1"/>
     </row>
-    <row r="257" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>51</v>
       </c>
@@ -41107,7 +41279,7 @@
       </c>
       <c r="AY257" s="1"/>
     </row>
-    <row r="258" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>51</v>
       </c>
@@ -41258,7 +41430,7 @@
       </c>
       <c r="AY258" s="1"/>
     </row>
-    <row r="259" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>51</v>
       </c>
@@ -41408,7 +41580,7 @@
       </c>
       <c r="AY259" s="1"/>
     </row>
-    <row r="260" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>51</v>
       </c>
@@ -41559,7 +41731,7 @@
       </c>
       <c r="AY260" s="1"/>
     </row>
-    <row r="261" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>51</v>
       </c>
@@ -41710,7 +41882,7 @@
       </c>
       <c r="AY261" s="1"/>
     </row>
-    <row r="262" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>51</v>
       </c>
@@ -41861,7 +42033,7 @@
       </c>
       <c r="AY262" s="1"/>
     </row>
-    <row r="263" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>51</v>
       </c>
@@ -42012,7 +42184,7 @@
       </c>
       <c r="AY263" s="1"/>
     </row>
-    <row r="264" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>51</v>
       </c>
@@ -42163,7 +42335,7 @@
       </c>
       <c r="AY264" s="1"/>
     </row>
-    <row r="265" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>51</v>
       </c>
@@ -42314,7 +42486,7 @@
       </c>
       <c r="AY265" s="1"/>
     </row>
-    <row r="266" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>51</v>
       </c>
@@ -42464,7 +42636,7 @@
       </c>
       <c r="AY266" s="1"/>
     </row>
-    <row r="267" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>51</v>
       </c>
@@ -42614,7 +42786,7 @@
       </c>
       <c r="AY267" s="1"/>
     </row>
-    <row r="268" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>51</v>
       </c>
@@ -42765,7 +42937,7 @@
       </c>
       <c r="AY268" s="1"/>
     </row>
-    <row r="269" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="8">
         <v>51</v>
       </c>
@@ -42916,7 +43088,7 @@
       </c>
       <c r="AY269" s="8"/>
     </row>
-    <row r="270" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>55</v>
       </c>
@@ -43054,7 +43226,7 @@
       <c r="AX270" s="1"/>
       <c r="AY270" s="1"/>
     </row>
-    <row r="271" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="8">
         <v>55</v>
       </c>
@@ -43192,7 +43364,7 @@
       <c r="AX271" s="8"/>
       <c r="AY271" s="8"/>
     </row>
-    <row r="272" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>56</v>
       </c>
@@ -43337,7 +43509,7 @@
       <c r="AX272" s="1"/>
       <c r="AY272" s="1"/>
     </row>
-    <row r="273" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>56</v>
       </c>
@@ -43481,250 +43653,4695 @@
       <c r="AX273" s="1"/>
       <c r="AY273" s="1"/>
     </row>
-    <row r="274" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A274" s="1"/>
-      <c r="K274" s="5"/>
-      <c r="L274" s="5"/>
-      <c r="Q274" s="1"/>
-      <c r="R274" s="1"/>
-      <c r="S274" s="1"/>
-      <c r="T274" s="1"/>
-      <c r="U274" s="1"/>
-      <c r="V274" s="1"/>
-      <c r="Y274" s="15"/>
-      <c r="Z274" s="15"/>
-      <c r="AD274" s="1"/>
-      <c r="AE274" s="1"/>
-      <c r="AK274" s="1"/>
-      <c r="AL274" s="1"/>
-      <c r="AM274" s="1"/>
-      <c r="AN274" s="1"/>
-      <c r="AO274" s="1"/>
-      <c r="AP274" s="1"/>
-      <c r="AQ274" s="1"/>
-      <c r="AR274" s="1"/>
-      <c r="AS274" s="1"/>
-      <c r="AV274" s="1"/>
+    <row r="274" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="62">
+        <v>57</v>
+      </c>
+      <c r="B274" s="63" t="s">
+        <v>981</v>
+      </c>
+      <c r="C274" s="63" t="s">
+        <v>982</v>
+      </c>
+      <c r="D274" s="63" t="s">
+        <v>983</v>
+      </c>
+      <c r="E274" s="63" t="s">
+        <v>984</v>
+      </c>
+      <c r="F274" s="63"/>
+      <c r="G274" s="63"/>
+      <c r="H274" s="63"/>
+      <c r="I274" s="63"/>
+      <c r="J274" s="63"/>
+      <c r="K274" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L274" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M274" s="63" t="s">
+        <v>985</v>
+      </c>
+      <c r="N274" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O274" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P274" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q274" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R274" s="62">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S274" s="62"/>
+      <c r="T274" s="62">
+        <v>1.25</v>
+      </c>
+      <c r="U274" s="62"/>
+      <c r="V274" s="62">
+        <v>6.9</v>
+      </c>
+      <c r="W274" s="63"/>
+      <c r="X274" s="63">
+        <v>74.8</v>
+      </c>
+      <c r="Y274" s="64"/>
+      <c r="Z274" s="64"/>
+      <c r="AA274" s="63"/>
+      <c r="AB274" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC274" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AD274" s="62" t="s">
+        <v>408</v>
+      </c>
+      <c r="AE274" s="62" t="s">
+        <v>408</v>
+      </c>
+      <c r="AF274" s="63" t="s">
+        <v>923</v>
+      </c>
+      <c r="AG274" s="63" t="s">
+        <v>966</v>
+      </c>
+      <c r="AH274" s="63" t="s">
+        <v>539</v>
+      </c>
+      <c r="AI274" s="63" t="s">
+        <v>987</v>
+      </c>
+      <c r="AJ274" s="63"/>
+      <c r="AK274" s="62">
+        <v>6.9</v>
+      </c>
+      <c r="AL274" s="62">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AM274" s="63">
+        <v>31.29</v>
+      </c>
+      <c r="AN274" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO274" s="62"/>
+      <c r="AP274" s="62">
+        <v>18.89</v>
+      </c>
+      <c r="AQ274" s="62"/>
+      <c r="AR274" s="62"/>
+      <c r="AS274" s="62"/>
+      <c r="AT274" s="63"/>
+      <c r="AU274" s="63">
+        <v>39.629274528603389</v>
+      </c>
+      <c r="AV274" s="62" t="s">
+        <v>101</v>
+      </c>
       <c r="AX274" s="1"/>
       <c r="AY274" s="1"/>
     </row>
-    <row r="275" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A275" s="1"/>
-      <c r="K275" s="5"/>
-      <c r="L275" s="5"/>
-      <c r="Q275" s="1"/>
-      <c r="R275" s="1"/>
-      <c r="S275" s="1"/>
-      <c r="T275" s="1"/>
-      <c r="U275" s="1"/>
-      <c r="V275" s="1"/>
-      <c r="Y275" s="15"/>
-      <c r="Z275" s="15"/>
-      <c r="AD275" s="1"/>
-      <c r="AE275" s="1"/>
-      <c r="AK275" s="1"/>
-      <c r="AL275" s="1"/>
-      <c r="AM275" s="1"/>
-      <c r="AN275" s="1"/>
-      <c r="AO275" s="1"/>
-      <c r="AP275" s="1"/>
-      <c r="AQ275" s="1"/>
-      <c r="AR275" s="1"/>
-      <c r="AS275" s="1"/>
-      <c r="AV275" s="1"/>
+    <row r="275" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="62">
+        <v>57</v>
+      </c>
+      <c r="B275" s="63" t="s">
+        <v>981</v>
+      </c>
+      <c r="C275" s="63" t="s">
+        <v>982</v>
+      </c>
+      <c r="D275" s="63" t="s">
+        <v>983</v>
+      </c>
+      <c r="E275" s="63" t="s">
+        <v>984</v>
+      </c>
+      <c r="F275" s="63"/>
+      <c r="G275" s="63"/>
+      <c r="H275" s="63"/>
+      <c r="I275" s="63"/>
+      <c r="J275" s="63"/>
+      <c r="K275" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L275" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M275" s="63" t="s">
+        <v>985</v>
+      </c>
+      <c r="N275" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O275" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P275" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q275" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R275" s="62">
+        <v>7.5</v>
+      </c>
+      <c r="S275" s="62"/>
+      <c r="T275" s="62">
+        <v>1.75</v>
+      </c>
+      <c r="U275" s="62"/>
+      <c r="V275" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="W275" s="63"/>
+      <c r="X275" s="63">
+        <v>105.2</v>
+      </c>
+      <c r="Y275" s="64"/>
+      <c r="Z275" s="64"/>
+      <c r="AA275" s="63"/>
+      <c r="AB275" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC275" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AD275" s="62" t="s">
+        <v>988</v>
+      </c>
+      <c r="AE275" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF275" s="63" t="s">
+        <v>923</v>
+      </c>
+      <c r="AG275" s="63" t="s">
+        <v>966</v>
+      </c>
+      <c r="AH275" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI275" s="63" t="s">
+        <v>914</v>
+      </c>
+      <c r="AJ275" s="63"/>
+      <c r="AK275" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="AL275" s="62">
+        <v>7.5</v>
+      </c>
+      <c r="AM275" s="63">
+        <v>31.29</v>
+      </c>
+      <c r="AN275" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO275" s="62"/>
+      <c r="AP275" s="62">
+        <v>27.13</v>
+      </c>
+      <c r="AQ275" s="62"/>
+      <c r="AR275" s="62"/>
+      <c r="AS275" s="62"/>
+      <c r="AT275" s="63"/>
+      <c r="AU275" s="63">
+        <v>13.294982422499203</v>
+      </c>
+      <c r="AV275" s="62" t="s">
+        <v>101</v>
+      </c>
       <c r="AX275" s="1"/>
       <c r="AY275" s="1"/>
     </row>
-    <row r="276" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A276" s="1"/>
-      <c r="K276" s="5"/>
-      <c r="L276" s="5"/>
-      <c r="Q276" s="1"/>
-      <c r="R276" s="1"/>
-      <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
-      <c r="U276" s="1"/>
-      <c r="V276" s="1"/>
-      <c r="Y276" s="15"/>
-      <c r="Z276" s="15"/>
-      <c r="AD276" s="1"/>
-      <c r="AE276" s="1"/>
-      <c r="AK276" s="1"/>
-      <c r="AL276" s="1"/>
-      <c r="AM276" s="1"/>
-      <c r="AN276" s="1"/>
-      <c r="AO276" s="1"/>
-      <c r="AP276" s="1"/>
-      <c r="AQ276" s="1"/>
-      <c r="AR276" s="1"/>
-      <c r="AS276" s="1"/>
-      <c r="AV276" s="1"/>
+    <row r="276" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="62">
+        <v>57</v>
+      </c>
+      <c r="B276" s="63" t="s">
+        <v>981</v>
+      </c>
+      <c r="C276" s="63" t="s">
+        <v>982</v>
+      </c>
+      <c r="D276" s="63" t="s">
+        <v>983</v>
+      </c>
+      <c r="E276" s="63" t="s">
+        <v>984</v>
+      </c>
+      <c r="F276" s="63"/>
+      <c r="G276" s="63"/>
+      <c r="H276" s="63"/>
+      <c r="I276" s="63"/>
+      <c r="J276" s="63"/>
+      <c r="K276" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L276" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M276" s="63" t="s">
+        <v>985</v>
+      </c>
+      <c r="N276" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O276" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P276" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q276" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R276" s="62">
+        <v>7.5</v>
+      </c>
+      <c r="S276" s="62"/>
+      <c r="T276" s="62">
+        <v>1.75</v>
+      </c>
+      <c r="U276" s="62"/>
+      <c r="V276" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="W276" s="63"/>
+      <c r="X276" s="63">
+        <v>105.2</v>
+      </c>
+      <c r="Y276" s="64"/>
+      <c r="Z276" s="64"/>
+      <c r="AA276" s="63"/>
+      <c r="AB276" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC276" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AD276" s="62" t="s">
+        <v>989</v>
+      </c>
+      <c r="AE276" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF276" s="63" t="s">
+        <v>923</v>
+      </c>
+      <c r="AG276" s="63" t="s">
+        <v>966</v>
+      </c>
+      <c r="AH276" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI276" s="63" t="s">
+        <v>914</v>
+      </c>
+      <c r="AJ276" s="63"/>
+      <c r="AK276" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="AL276" s="62">
+        <v>7.5</v>
+      </c>
+      <c r="AM276" s="63">
+        <v>31.29</v>
+      </c>
+      <c r="AN276" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO276" s="62"/>
+      <c r="AP276" s="62">
+        <v>34.67</v>
+      </c>
+      <c r="AQ276" s="62"/>
+      <c r="AR276" s="62"/>
+      <c r="AS276" s="62"/>
+      <c r="AT276" s="63"/>
+      <c r="AU276" s="63">
+        <v>-10.802173218280608</v>
+      </c>
+      <c r="AV276" s="62" t="s">
+        <v>101</v>
+      </c>
       <c r="AX276" s="1"/>
       <c r="AY276" s="1"/>
     </row>
-    <row r="277" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="1"/>
-      <c r="K277" s="5"/>
-      <c r="L277" s="5"/>
-      <c r="Q277" s="1"/>
-      <c r="R277" s="1"/>
-      <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
-      <c r="U277" s="1"/>
-      <c r="V277" s="1"/>
-      <c r="Y277" s="15"/>
-      <c r="Z277" s="15"/>
-      <c r="AD277" s="1"/>
-      <c r="AE277" s="1"/>
-      <c r="AK277" s="1"/>
-      <c r="AL277" s="1"/>
-      <c r="AM277" s="1"/>
-      <c r="AN277" s="1"/>
-      <c r="AO277" s="1"/>
-      <c r="AP277" s="1"/>
-      <c r="AQ277" s="1"/>
-      <c r="AR277" s="1"/>
-      <c r="AS277" s="1"/>
-      <c r="AV277" s="1"/>
+    <row r="277" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="62">
+        <v>57</v>
+      </c>
+      <c r="B277" s="63" t="s">
+        <v>981</v>
+      </c>
+      <c r="C277" s="63" t="s">
+        <v>982</v>
+      </c>
+      <c r="D277" s="63" t="s">
+        <v>983</v>
+      </c>
+      <c r="E277" s="63" t="s">
+        <v>984</v>
+      </c>
+      <c r="F277" s="63"/>
+      <c r="G277" s="63"/>
+      <c r="H277" s="63"/>
+      <c r="I277" s="63"/>
+      <c r="J277" s="63"/>
+      <c r="K277" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L277" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M277" s="63" t="s">
+        <v>985</v>
+      </c>
+      <c r="N277" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O277" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P277" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q277" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R277" s="62">
+        <v>7.9</v>
+      </c>
+      <c r="S277" s="62"/>
+      <c r="T277" s="62"/>
+      <c r="U277" s="62"/>
+      <c r="V277" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="W277" s="63"/>
+      <c r="X277" s="63"/>
+      <c r="Y277" s="64"/>
+      <c r="Z277" s="64"/>
+      <c r="AA277" s="63"/>
+      <c r="AB277" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC277" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AD277" s="62" t="s">
+        <v>990</v>
+      </c>
+      <c r="AE277" s="62" t="s">
+        <v>917</v>
+      </c>
+      <c r="AF277" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG277" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH277" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI277" s="63" t="s">
+        <v>914</v>
+      </c>
+      <c r="AJ277" s="63"/>
+      <c r="AK277" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="AL277" s="62">
+        <v>7.9</v>
+      </c>
+      <c r="AM277" s="62">
+        <v>27.13</v>
+      </c>
+      <c r="AN277" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO277" s="62"/>
+      <c r="AP277" s="62">
+        <v>14.01</v>
+      </c>
+      <c r="AQ277" s="62"/>
+      <c r="AR277" s="62"/>
+      <c r="AS277" s="62"/>
+      <c r="AT277" s="63"/>
+      <c r="AU277" s="63">
+        <v>48.359749354957614</v>
+      </c>
+      <c r="AV277" s="62" t="s">
+        <v>101</v>
+      </c>
       <c r="AX277" s="1"/>
       <c r="AY277" s="1"/>
     </row>
-    <row r="278" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="1"/>
-      <c r="K278" s="5"/>
-      <c r="L278" s="5"/>
-      <c r="Q278" s="1"/>
-      <c r="R278" s="1"/>
-      <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
-      <c r="U278" s="1"/>
-      <c r="V278" s="1"/>
-      <c r="Y278" s="15"/>
-      <c r="Z278" s="15"/>
-      <c r="AD278" s="1"/>
-      <c r="AE278" s="1"/>
-      <c r="AK278" s="1"/>
-      <c r="AL278" s="1"/>
-      <c r="AM278" s="1"/>
-      <c r="AN278" s="1"/>
-      <c r="AO278" s="1"/>
-      <c r="AP278" s="1"/>
-      <c r="AQ278" s="1"/>
-      <c r="AR278" s="1"/>
-      <c r="AS278" s="1"/>
-      <c r="AV278" s="1"/>
+    <row r="278" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="62">
+        <v>57</v>
+      </c>
+      <c r="B278" s="63" t="s">
+        <v>981</v>
+      </c>
+      <c r="C278" s="63" t="s">
+        <v>982</v>
+      </c>
+      <c r="D278" s="63" t="s">
+        <v>983</v>
+      </c>
+      <c r="E278" s="63" t="s">
+        <v>984</v>
+      </c>
+      <c r="F278" s="63"/>
+      <c r="G278" s="63"/>
+      <c r="H278" s="63"/>
+      <c r="I278" s="63"/>
+      <c r="J278" s="63"/>
+      <c r="K278" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L278" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M278" s="63" t="s">
+        <v>985</v>
+      </c>
+      <c r="N278" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O278" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P278" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q278" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R278" s="62">
+        <v>1.8</v>
+      </c>
+      <c r="S278" s="62"/>
+      <c r="T278" s="62"/>
+      <c r="U278" s="62"/>
+      <c r="V278" s="62">
+        <v>7.2</v>
+      </c>
+      <c r="W278" s="63"/>
+      <c r="X278" s="63"/>
+      <c r="Y278" s="64"/>
+      <c r="Z278" s="64"/>
+      <c r="AA278" s="63"/>
+      <c r="AB278" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC278" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AD278" s="62" t="s">
+        <v>988</v>
+      </c>
+      <c r="AE278" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF278" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG278" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH278" s="63" t="s">
+        <v>539</v>
+      </c>
+      <c r="AI278" s="63" t="s">
+        <v>987</v>
+      </c>
+      <c r="AJ278" s="63"/>
+      <c r="AK278" s="62">
+        <v>7.2</v>
+      </c>
+      <c r="AL278" s="62">
+        <v>1.8</v>
+      </c>
+      <c r="AM278" s="62">
+        <v>27.13</v>
+      </c>
+      <c r="AN278" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO278" s="62"/>
+      <c r="AP278" s="62">
+        <v>7.89</v>
+      </c>
+      <c r="AQ278" s="62"/>
+      <c r="AR278" s="62"/>
+      <c r="AS278" s="62"/>
+      <c r="AT278" s="63"/>
+      <c r="AU278" s="63">
+        <v>70.917803169922593</v>
+      </c>
+      <c r="AV278" s="62" t="s">
+        <v>101</v>
+      </c>
       <c r="AX278" s="1"/>
       <c r="AY278" s="1"/>
     </row>
-    <row r="279" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A279" s="1"/>
-      <c r="K279" s="5"/>
-      <c r="L279" s="5"/>
-      <c r="Q279" s="1"/>
-      <c r="R279" s="1"/>
-      <c r="S279" s="1"/>
-      <c r="T279" s="1"/>
-      <c r="U279" s="1"/>
-      <c r="V279" s="1"/>
-      <c r="Y279" s="15"/>
-      <c r="Z279" s="15"/>
-      <c r="AD279" s="1"/>
-      <c r="AE279" s="1"/>
-      <c r="AK279" s="1"/>
-      <c r="AL279" s="1"/>
-      <c r="AM279" s="1"/>
-      <c r="AN279" s="1"/>
-      <c r="AO279" s="1"/>
-      <c r="AP279" s="1"/>
-      <c r="AQ279" s="1"/>
-      <c r="AR279" s="1"/>
-      <c r="AS279" s="1"/>
-      <c r="AV279" s="1"/>
+    <row r="279" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="62">
+        <v>57</v>
+      </c>
+      <c r="B279" s="63" t="s">
+        <v>981</v>
+      </c>
+      <c r="C279" s="63" t="s">
+        <v>982</v>
+      </c>
+      <c r="D279" s="63" t="s">
+        <v>983</v>
+      </c>
+      <c r="E279" s="63" t="s">
+        <v>984</v>
+      </c>
+      <c r="F279" s="63"/>
+      <c r="G279" s="63"/>
+      <c r="H279" s="63"/>
+      <c r="I279" s="63"/>
+      <c r="J279" s="63"/>
+      <c r="K279" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L279" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M279" s="63" t="s">
+        <v>985</v>
+      </c>
+      <c r="N279" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O279" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P279" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q279" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R279" s="62">
+        <v>1.8</v>
+      </c>
+      <c r="S279" s="62"/>
+      <c r="T279" s="62"/>
+      <c r="U279" s="62"/>
+      <c r="V279" s="62">
+        <v>7.2</v>
+      </c>
+      <c r="W279" s="63"/>
+      <c r="X279" s="63"/>
+      <c r="Y279" s="64"/>
+      <c r="Z279" s="64"/>
+      <c r="AA279" s="63"/>
+      <c r="AB279" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC279" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AD279" s="62" t="s">
+        <v>990</v>
+      </c>
+      <c r="AE279" s="62" t="s">
+        <v>917</v>
+      </c>
+      <c r="AF279" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG279" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH279" s="63" t="s">
+        <v>539</v>
+      </c>
+      <c r="AI279" s="63" t="s">
+        <v>987</v>
+      </c>
+      <c r="AJ279" s="63"/>
+      <c r="AK279" s="62">
+        <v>7.2</v>
+      </c>
+      <c r="AL279" s="62">
+        <v>1.8</v>
+      </c>
+      <c r="AM279" s="62">
+        <v>27.13</v>
+      </c>
+      <c r="AN279" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO279" s="62"/>
+      <c r="AP279" s="62">
+        <v>7.75</v>
+      </c>
+      <c r="AQ279" s="62"/>
+      <c r="AR279" s="62"/>
+      <c r="AS279" s="62"/>
+      <c r="AT279" s="63"/>
+      <c r="AU279" s="63">
+        <v>71.433837080722441</v>
+      </c>
+      <c r="AV279" s="62" t="s">
+        <v>101</v>
+      </c>
       <c r="AX279" s="1"/>
       <c r="AY279" s="1"/>
     </row>
-    <row r="280" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="1"/>
-      <c r="K280" s="5"/>
-      <c r="L280" s="5"/>
-      <c r="Q280" s="1"/>
-      <c r="R280" s="1"/>
-      <c r="S280" s="1"/>
-      <c r="T280" s="1"/>
-      <c r="U280" s="1"/>
-      <c r="V280" s="1"/>
-      <c r="Y280" s="15"/>
-      <c r="Z280" s="15"/>
-      <c r="AD280" s="1"/>
-      <c r="AE280" s="1"/>
-      <c r="AK280" s="1"/>
-      <c r="AL280" s="1"/>
-      <c r="AM280" s="1"/>
-      <c r="AN280" s="1"/>
-      <c r="AO280" s="1"/>
-      <c r="AP280" s="1"/>
-      <c r="AQ280" s="1"/>
-      <c r="AR280" s="1"/>
-      <c r="AS280" s="1"/>
-      <c r="AV280" s="1"/>
+    <row r="280" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="62">
+        <v>58</v>
+      </c>
+      <c r="B280" s="63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C280" s="63" t="s">
+        <v>992</v>
+      </c>
+      <c r="D280" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E280" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F280" s="63"/>
+      <c r="G280" s="63"/>
+      <c r="H280" s="63">
+        <v>768</v>
+      </c>
+      <c r="I280" s="63">
+        <v>77</v>
+      </c>
+      <c r="J280" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K280" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L280" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M280" s="63" t="s">
+        <v>993</v>
+      </c>
+      <c r="N280" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O280" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P280" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q280" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R280" s="62">
+        <v>6.5</v>
+      </c>
+      <c r="S280" s="62"/>
+      <c r="T280" s="62"/>
+      <c r="U280" s="62"/>
+      <c r="V280" s="62">
+        <v>7.2</v>
+      </c>
+      <c r="W280" s="63"/>
+      <c r="X280" s="63">
+        <v>84.8</v>
+      </c>
+      <c r="Y280" s="64">
+        <v>41730</v>
+      </c>
+      <c r="Z280" s="64"/>
+      <c r="AA280" s="63"/>
+      <c r="AB280" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC280" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD280" s="62" t="s">
+        <v>994</v>
+      </c>
+      <c r="AE280" s="62" t="s">
+        <v>995</v>
+      </c>
+      <c r="AF280" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG280" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH280" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI280" s="63" t="s">
+        <v>914</v>
+      </c>
+      <c r="AJ280" s="63"/>
+      <c r="AK280" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="AL280" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM280" s="62"/>
+      <c r="AN280" s="62"/>
+      <c r="AO280" s="62"/>
+      <c r="AP280" s="62"/>
+      <c r="AQ280" s="62"/>
+      <c r="AR280" s="62"/>
+      <c r="AS280" s="62"/>
+      <c r="AT280" s="63"/>
+      <c r="AU280" s="63">
+        <v>59</v>
+      </c>
+      <c r="AV280" s="62"/>
       <c r="AX280" s="1"/>
       <c r="AY280" s="1"/>
     </row>
-    <row r="281" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="1"/>
-      <c r="K281" s="5"/>
-      <c r="L281" s="5"/>
-      <c r="Q281" s="1"/>
-      <c r="R281" s="1"/>
-      <c r="S281" s="1"/>
-      <c r="T281" s="1"/>
-      <c r="U281" s="1"/>
-      <c r="V281" s="1"/>
-      <c r="Y281" s="15"/>
-      <c r="Z281" s="15"/>
-      <c r="AD281" s="1"/>
-      <c r="AE281" s="1"/>
-      <c r="AK281" s="1"/>
-      <c r="AL281" s="1"/>
-      <c r="AM281" s="1"/>
-      <c r="AN281" s="1"/>
-      <c r="AO281" s="1"/>
-      <c r="AP281" s="1"/>
-      <c r="AQ281" s="1"/>
-      <c r="AR281" s="1"/>
-      <c r="AS281" s="1"/>
-      <c r="AV281" s="1"/>
+    <row r="281" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="62">
+        <v>58</v>
+      </c>
+      <c r="B281" s="63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C281" s="63" t="s">
+        <v>992</v>
+      </c>
+      <c r="D281" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E281" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F281" s="63"/>
+      <c r="G281" s="63"/>
+      <c r="H281" s="63">
+        <v>768</v>
+      </c>
+      <c r="I281" s="63">
+        <v>77</v>
+      </c>
+      <c r="J281" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K281" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L281" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M281" s="63" t="s">
+        <v>993</v>
+      </c>
+      <c r="N281" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O281" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P281" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q281" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R281" s="62">
+        <v>6.4</v>
+      </c>
+      <c r="S281" s="62"/>
+      <c r="T281" s="62"/>
+      <c r="U281" s="62"/>
+      <c r="V281" s="62">
+        <v>5.6</v>
+      </c>
+      <c r="W281" s="63"/>
+      <c r="X281" s="63">
+        <v>84.8</v>
+      </c>
+      <c r="Y281" s="64">
+        <v>41730</v>
+      </c>
+      <c r="Z281" s="64"/>
+      <c r="AA281" s="63"/>
+      <c r="AB281" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC281" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD281" s="62" t="s">
+        <v>994</v>
+      </c>
+      <c r="AE281" s="62"/>
+      <c r="AF281" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG281" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH281" s="63" t="s">
+        <v>996</v>
+      </c>
+      <c r="AI281" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ281" s="63">
+        <v>0.25</v>
+      </c>
+      <c r="AK281" s="62">
+        <v>5.6</v>
+      </c>
+      <c r="AL281" s="62">
+        <v>6.4</v>
+      </c>
+      <c r="AM281" s="62"/>
+      <c r="AN281" s="62"/>
+      <c r="AO281" s="62"/>
+      <c r="AP281" s="62"/>
+      <c r="AQ281" s="62"/>
+      <c r="AR281" s="62"/>
+      <c r="AS281" s="62"/>
+      <c r="AT281" s="63"/>
+      <c r="AU281" s="63">
+        <v>88</v>
+      </c>
+      <c r="AV281" s="62"/>
       <c r="AX281" s="1"/>
       <c r="AY281" s="1"/>
     </row>
-    <row r="282" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="1"/>
-      <c r="K282" s="5"/>
-      <c r="L282" s="5"/>
-      <c r="Q282" s="1"/>
-      <c r="R282" s="1"/>
-      <c r="S282" s="1"/>
-      <c r="T282" s="1"/>
-      <c r="U282" s="1"/>
-      <c r="V282" s="1"/>
-      <c r="Y282" s="15"/>
-      <c r="Z282" s="15"/>
-      <c r="AD282" s="1"/>
-      <c r="AE282" s="1"/>
-      <c r="AK282" s="1"/>
-      <c r="AL282" s="1"/>
-      <c r="AM282" s="1"/>
-      <c r="AN282" s="1"/>
-      <c r="AO282" s="1"/>
-      <c r="AP282" s="1"/>
-      <c r="AQ282" s="1"/>
-      <c r="AR282" s="1"/>
-      <c r="AS282" s="1"/>
-      <c r="AV282" s="1"/>
+    <row r="282" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="62">
+        <v>58</v>
+      </c>
+      <c r="B282" s="63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C282" s="63" t="s">
+        <v>992</v>
+      </c>
+      <c r="D282" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E282" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F282" s="63"/>
+      <c r="G282" s="63"/>
+      <c r="H282" s="63">
+        <v>768</v>
+      </c>
+      <c r="I282" s="63">
+        <v>77</v>
+      </c>
+      <c r="J282" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K282" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L282" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M282" s="63" t="s">
+        <v>993</v>
+      </c>
+      <c r="N282" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O282" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P282" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q282" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R282" s="62">
+        <v>6.4</v>
+      </c>
+      <c r="S282" s="62"/>
+      <c r="T282" s="62"/>
+      <c r="U282" s="62"/>
+      <c r="V282" s="62">
+        <v>7.2</v>
+      </c>
+      <c r="W282" s="63"/>
+      <c r="X282" s="63">
+        <v>80</v>
+      </c>
+      <c r="Y282" s="64">
+        <v>41730</v>
+      </c>
+      <c r="Z282" s="64"/>
+      <c r="AA282" s="63"/>
+      <c r="AB282" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC282" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD282" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE282" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF282" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG282" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH282" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI282" s="63" t="s">
+        <v>914</v>
+      </c>
+      <c r="AJ282" s="63"/>
+      <c r="AK282" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="AL282" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM282" s="62"/>
+      <c r="AN282" s="62"/>
+      <c r="AO282" s="62"/>
+      <c r="AP282" s="62"/>
+      <c r="AQ282" s="62"/>
+      <c r="AR282" s="62"/>
+      <c r="AS282" s="62"/>
+      <c r="AT282" s="63"/>
+      <c r="AU282" s="63">
+        <v>96</v>
+      </c>
+      <c r="AV282" s="62"/>
       <c r="AX282" s="1"/>
       <c r="AY282" s="1"/>
     </row>
-    <row r="283" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="283" spans="1:51" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="62">
+        <v>58</v>
+      </c>
+      <c r="B283" s="63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C283" s="63" t="s">
+        <v>992</v>
+      </c>
+      <c r="D283" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E283" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F283" s="61"/>
+      <c r="G283" s="61"/>
+      <c r="H283" s="63">
+        <v>768</v>
+      </c>
+      <c r="I283" s="63">
+        <v>77</v>
+      </c>
+      <c r="J283" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K283" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L283" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M283" s="63" t="s">
+        <v>993</v>
+      </c>
+      <c r="N283" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O283" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P283" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q283" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R283" s="62">
+        <v>6.4</v>
+      </c>
+      <c r="S283" s="61"/>
+      <c r="T283" s="61"/>
+      <c r="U283" s="61"/>
+      <c r="V283" s="62">
+        <v>5.7</v>
+      </c>
+      <c r="W283" s="61"/>
+      <c r="X283" s="63">
+        <v>84.8</v>
+      </c>
+      <c r="Y283" s="64">
+        <v>41760</v>
+      </c>
+      <c r="Z283" s="61"/>
+      <c r="AA283" s="61"/>
+      <c r="AB283" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC283" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD283" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE283" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF283" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG283" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH283" s="63" t="s">
+        <v>998</v>
+      </c>
+      <c r="AI283" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ283" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="AK283" s="62">
+        <v>5.7</v>
+      </c>
+      <c r="AL283" s="62">
+        <v>6.5</v>
+      </c>
+      <c r="AM283" s="61"/>
+      <c r="AN283" s="61"/>
+      <c r="AO283" s="61"/>
+      <c r="AP283" s="61"/>
+      <c r="AQ283" s="61"/>
+      <c r="AR283" s="61"/>
+      <c r="AS283" s="61"/>
+      <c r="AT283" s="61"/>
+      <c r="AU283" s="63">
+        <v>74</v>
+      </c>
+      <c r="AV283" s="61"/>
+    </row>
+    <row r="284" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="62">
+        <v>58</v>
+      </c>
+      <c r="B284" s="63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C284" s="63" t="s">
+        <v>992</v>
+      </c>
+      <c r="D284" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E284" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F284" s="61"/>
+      <c r="G284" s="61"/>
+      <c r="H284" s="63">
+        <v>786</v>
+      </c>
+      <c r="I284" s="63">
+        <v>69</v>
+      </c>
+      <c r="J284" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K284" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L284" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M284" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N284" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O284" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P284" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q284" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R284" s="62">
+        <v>6.2</v>
+      </c>
+      <c r="S284" s="61"/>
+      <c r="T284" s="61"/>
+      <c r="U284" s="61"/>
+      <c r="V284" s="62">
+        <v>7.3</v>
+      </c>
+      <c r="W284" s="61"/>
+      <c r="X284" s="63">
+        <v>84.8</v>
+      </c>
+      <c r="Y284" s="64">
+        <v>41732</v>
+      </c>
+      <c r="Z284" s="61"/>
+      <c r="AA284" s="61"/>
+      <c r="AB284" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC284" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD284" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE284" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF284" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG284" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH284" s="63" t="s">
+        <v>998</v>
+      </c>
+      <c r="AI284" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ284" s="61"/>
+      <c r="AK284" s="62">
+        <v>6.5</v>
+      </c>
+      <c r="AL284" s="62">
+        <v>5.7</v>
+      </c>
+      <c r="AM284" s="61"/>
+      <c r="AN284" s="61"/>
+      <c r="AO284" s="61"/>
+      <c r="AP284" s="61"/>
+      <c r="AQ284" s="61"/>
+      <c r="AR284" s="61"/>
+      <c r="AS284" s="61"/>
+      <c r="AT284" s="61"/>
+      <c r="AU284" s="63">
+        <v>61</v>
+      </c>
+      <c r="AV284" s="61"/>
+    </row>
+    <row r="285" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="62">
+        <v>58</v>
+      </c>
+      <c r="B285" s="63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C285" s="63" t="s">
+        <v>992</v>
+      </c>
+      <c r="D285" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E285" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F285" s="61"/>
+      <c r="G285" s="61"/>
+      <c r="H285" s="63">
+        <v>786</v>
+      </c>
+      <c r="I285" s="63">
+        <v>69</v>
+      </c>
+      <c r="J285" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K285" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L285" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M285" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N285" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O285" s="63" t="s">
+        <v>999</v>
+      </c>
+      <c r="P285" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q285" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R285" s="62">
+        <v>3.5</v>
+      </c>
+      <c r="S285" s="61"/>
+      <c r="T285" s="61"/>
+      <c r="U285" s="61"/>
+      <c r="V285" s="62">
+        <v>7.6</v>
+      </c>
+      <c r="W285" s="61"/>
+      <c r="X285" s="63">
+        <v>79.5</v>
+      </c>
+      <c r="Y285" s="64">
+        <v>41732</v>
+      </c>
+      <c r="Z285" s="61"/>
+      <c r="AA285" s="61"/>
+      <c r="AB285" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC285" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD285" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE285" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF285" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG285" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH285" s="63" t="s">
+        <v>959</v>
+      </c>
+      <c r="AI285" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ285" s="61"/>
+      <c r="AK285" s="62">
+        <v>6.5</v>
+      </c>
+      <c r="AL285" s="62">
+        <v>4.3</v>
+      </c>
+      <c r="AM285" s="61"/>
+      <c r="AN285" s="61"/>
+      <c r="AO285" s="61"/>
+      <c r="AP285" s="61"/>
+      <c r="AQ285" s="61"/>
+      <c r="AR285" s="61"/>
+      <c r="AS285" s="61"/>
+      <c r="AT285" s="61"/>
+      <c r="AU285" s="63">
+        <v>57</v>
+      </c>
+      <c r="AV285" s="61"/>
+    </row>
+    <row r="286" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="62">
+        <v>58</v>
+      </c>
+      <c r="B286" s="63" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C286" s="63" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D286" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E286" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F286" s="61"/>
+      <c r="G286" s="61"/>
+      <c r="H286" s="63">
+        <v>786</v>
+      </c>
+      <c r="I286" s="63">
+        <v>69</v>
+      </c>
+      <c r="J286" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K286" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L286" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M286" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N286" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O286" s="63" t="s">
+        <v>1002</v>
+      </c>
+      <c r="P286" s="63" t="s">
+        <v>1003</v>
+      </c>
+      <c r="Q286" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R286" s="62">
+        <v>1.4</v>
+      </c>
+      <c r="S286" s="61"/>
+      <c r="T286" s="61"/>
+      <c r="U286" s="61"/>
+      <c r="V286" s="62">
+        <v>7.2</v>
+      </c>
+      <c r="W286" s="61"/>
+      <c r="X286" s="63">
+        <v>78.8</v>
+      </c>
+      <c r="Y286" s="64">
+        <v>41732</v>
+      </c>
+      <c r="Z286" s="61"/>
+      <c r="AA286" s="61"/>
+      <c r="AB286" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC286" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD286" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE286" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF286" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG286" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH286" s="63" t="s">
+        <v>998</v>
+      </c>
+      <c r="AI286" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ286" s="61"/>
+      <c r="AK286" s="62">
+        <v>6</v>
+      </c>
+      <c r="AL286" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="AM286" s="61"/>
+      <c r="AN286" s="61"/>
+      <c r="AO286" s="61"/>
+      <c r="AP286" s="61"/>
+      <c r="AQ286" s="61"/>
+      <c r="AR286" s="61"/>
+      <c r="AS286" s="61"/>
+      <c r="AT286" s="61"/>
+      <c r="AU286" s="63">
+        <v>74</v>
+      </c>
+      <c r="AV286" s="61"/>
+    </row>
+    <row r="287" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="62">
+        <v>58</v>
+      </c>
+      <c r="B287" s="63" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C287" s="63" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D287" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E287" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F287" s="61"/>
+      <c r="G287" s="61"/>
+      <c r="H287" s="63">
+        <v>786</v>
+      </c>
+      <c r="I287" s="63">
+        <v>69</v>
+      </c>
+      <c r="J287" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K287" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L287" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M287" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N287" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O287" s="63" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P287" s="63" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q287" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R287" s="62">
+        <v>2.8</v>
+      </c>
+      <c r="S287" s="61"/>
+      <c r="T287" s="61"/>
+      <c r="U287" s="61"/>
+      <c r="V287" s="62">
+        <v>7.1</v>
+      </c>
+      <c r="W287" s="61"/>
+      <c r="X287" s="63">
+        <v>84.4</v>
+      </c>
+      <c r="Y287" s="64">
+        <v>41732</v>
+      </c>
+      <c r="Z287" s="61"/>
+      <c r="AA287" s="61"/>
+      <c r="AB287" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC287" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD287" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE287" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF287" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG287" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH287" s="63" t="s">
+        <v>998</v>
+      </c>
+      <c r="AI287" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ287" s="61"/>
+      <c r="AK287" s="62">
+        <v>5.4</v>
+      </c>
+      <c r="AL287" s="62">
+        <v>3</v>
+      </c>
+      <c r="AM287" s="61"/>
+      <c r="AN287" s="61"/>
+      <c r="AO287" s="61"/>
+      <c r="AP287" s="61"/>
+      <c r="AQ287" s="61"/>
+      <c r="AR287" s="61"/>
+      <c r="AS287" s="61"/>
+      <c r="AT287" s="61"/>
+      <c r="AU287" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="AV287" s="61"/>
+    </row>
+    <row r="288" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="62">
+        <v>58</v>
+      </c>
+      <c r="B288" s="63" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C288" s="63" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D288" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E288" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F288" s="61"/>
+      <c r="G288" s="61"/>
+      <c r="H288" s="63">
+        <v>786</v>
+      </c>
+      <c r="I288" s="63">
+        <v>69</v>
+      </c>
+      <c r="J288" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K288" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L288" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M288" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N288" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O288" s="63" t="s">
+        <v>1009</v>
+      </c>
+      <c r="P288" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q288" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R288" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="S288" s="61"/>
+      <c r="T288" s="61"/>
+      <c r="U288" s="61"/>
+      <c r="V288" s="62">
+        <v>8</v>
+      </c>
+      <c r="W288" s="61"/>
+      <c r="X288" s="63">
+        <v>79.5</v>
+      </c>
+      <c r="Y288" s="64">
+        <v>41732</v>
+      </c>
+      <c r="Z288" s="61"/>
+      <c r="AA288" s="61"/>
+      <c r="AB288" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC288" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD288" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE288" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF288" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG288" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH288" s="63" t="s">
+        <v>1010</v>
+      </c>
+      <c r="AI288" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ288" s="61"/>
+      <c r="AK288" s="62">
+        <v>6.6</v>
+      </c>
+      <c r="AL288" s="62">
+        <v>2.7</v>
+      </c>
+      <c r="AM288" s="61"/>
+      <c r="AN288" s="61"/>
+      <c r="AO288" s="61"/>
+      <c r="AP288" s="61"/>
+      <c r="AQ288" s="61"/>
+      <c r="AR288" s="61"/>
+      <c r="AS288" s="61"/>
+      <c r="AT288" s="61"/>
+      <c r="AU288" s="63">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="289" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A289" s="62">
+        <v>58</v>
+      </c>
+      <c r="B289" s="63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C289" s="63" t="s">
+        <v>992</v>
+      </c>
+      <c r="D289" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E289" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F289" s="61"/>
+      <c r="G289" s="61"/>
+      <c r="H289" s="63">
+        <v>786</v>
+      </c>
+      <c r="I289" s="63">
+        <v>69</v>
+      </c>
+      <c r="J289" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K289" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L289" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M289" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N289" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O289" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P289" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q289" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R289" s="62">
+        <v>6.2</v>
+      </c>
+      <c r="S289" s="61"/>
+      <c r="T289" s="61"/>
+      <c r="U289" s="61"/>
+      <c r="V289" s="62">
+        <v>7.4</v>
+      </c>
+      <c r="W289" s="61"/>
+      <c r="X289" s="63">
+        <v>84.8</v>
+      </c>
+      <c r="Y289" s="64">
+        <v>41759</v>
+      </c>
+      <c r="Z289" s="61"/>
+      <c r="AA289" s="61"/>
+      <c r="AB289" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC289" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD289" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE289" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF289" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG289" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH289" s="63" t="s">
+        <v>998</v>
+      </c>
+      <c r="AI289" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ289" s="61"/>
+      <c r="AK289" s="62">
+        <v>6.2</v>
+      </c>
+      <c r="AL289" s="62">
+        <v>5.7</v>
+      </c>
+      <c r="AM289" s="61"/>
+      <c r="AN289" s="61"/>
+      <c r="AO289" s="61"/>
+      <c r="AP289" s="61"/>
+      <c r="AQ289" s="61"/>
+      <c r="AR289" s="61"/>
+      <c r="AS289" s="61"/>
+      <c r="AT289" s="61"/>
+      <c r="AU289" s="63">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="290" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="62">
+        <v>58</v>
+      </c>
+      <c r="B290" s="63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C290" s="63" t="s">
+        <v>992</v>
+      </c>
+      <c r="D290" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E290" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F290" s="61"/>
+      <c r="G290" s="61"/>
+      <c r="H290" s="63">
+        <v>786</v>
+      </c>
+      <c r="I290" s="63">
+        <v>69</v>
+      </c>
+      <c r="J290" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K290" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L290" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M290" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N290" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O290" s="63" t="s">
+        <v>999</v>
+      </c>
+      <c r="P290" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q290" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R290" s="62">
+        <v>3.5</v>
+      </c>
+      <c r="S290" s="61"/>
+      <c r="T290" s="61"/>
+      <c r="U290" s="61"/>
+      <c r="V290" s="62">
+        <v>6.7</v>
+      </c>
+      <c r="W290" s="61"/>
+      <c r="X290" s="63">
+        <v>79.5</v>
+      </c>
+      <c r="Y290" s="64">
+        <v>41759</v>
+      </c>
+      <c r="Z290" s="61"/>
+      <c r="AA290" s="61"/>
+      <c r="AB290" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC290" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD290" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE290" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF290" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG290" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH290" s="63" t="s">
+        <v>959</v>
+      </c>
+      <c r="AI290" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ290" s="61"/>
+      <c r="AK290" s="62">
+        <v>3.2</v>
+      </c>
+      <c r="AL290" s="62">
+        <v>4.3</v>
+      </c>
+      <c r="AM290" s="61"/>
+      <c r="AN290" s="61"/>
+      <c r="AO290" s="61"/>
+      <c r="AP290" s="61"/>
+      <c r="AQ290" s="61"/>
+      <c r="AR290" s="61"/>
+      <c r="AS290" s="61"/>
+      <c r="AT290" s="61"/>
+      <c r="AU290" s="63">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="291" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="62">
+        <v>58</v>
+      </c>
+      <c r="B291" s="63" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C291" s="63" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D291" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E291" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F291" s="61"/>
+      <c r="G291" s="61"/>
+      <c r="H291" s="63">
+        <v>786</v>
+      </c>
+      <c r="I291" s="63">
+        <v>69</v>
+      </c>
+      <c r="J291" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K291" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L291" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M291" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N291" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O291" s="63" t="s">
+        <v>1002</v>
+      </c>
+      <c r="P291" s="63" t="s">
+        <v>1003</v>
+      </c>
+      <c r="Q291" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R291" s="62">
+        <v>1.4</v>
+      </c>
+      <c r="S291" s="61"/>
+      <c r="T291" s="61"/>
+      <c r="U291" s="61"/>
+      <c r="V291" s="62">
+        <v>7</v>
+      </c>
+      <c r="W291" s="61"/>
+      <c r="X291" s="63">
+        <v>78.8</v>
+      </c>
+      <c r="Y291" s="64">
+        <v>41759</v>
+      </c>
+      <c r="Z291" s="61"/>
+      <c r="AA291" s="61"/>
+      <c r="AB291" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC291" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD291" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE291" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF291" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG291" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH291" s="63" t="s">
+        <v>998</v>
+      </c>
+      <c r="AI291" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ291" s="61"/>
+      <c r="AK291" s="62">
+        <v>6.1</v>
+      </c>
+      <c r="AL291" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="AM291" s="61"/>
+      <c r="AN291" s="61"/>
+      <c r="AO291" s="61"/>
+      <c r="AP291" s="61"/>
+      <c r="AQ291" s="61"/>
+      <c r="AR291" s="61"/>
+      <c r="AS291" s="61"/>
+      <c r="AT291" s="61"/>
+      <c r="AU291" s="63">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="292" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="62">
+        <v>58</v>
+      </c>
+      <c r="B292" s="63" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C292" s="63" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D292" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E292" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F292" s="61"/>
+      <c r="G292" s="61"/>
+      <c r="H292" s="63">
+        <v>786</v>
+      </c>
+      <c r="I292" s="63">
+        <v>69</v>
+      </c>
+      <c r="J292" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K292" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L292" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M292" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N292" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O292" s="63" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P292" s="63" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q292" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R292" s="62">
+        <v>2.8</v>
+      </c>
+      <c r="S292" s="61"/>
+      <c r="T292" s="61"/>
+      <c r="U292" s="61"/>
+      <c r="V292" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="W292" s="61"/>
+      <c r="X292" s="63">
+        <v>84.4</v>
+      </c>
+      <c r="Y292" s="64">
+        <v>41759</v>
+      </c>
+      <c r="Z292" s="61"/>
+      <c r="AA292" s="61"/>
+      <c r="AB292" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC292" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD292" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE292" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF292" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG292" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH292" s="63" t="s">
+        <v>998</v>
+      </c>
+      <c r="AI292" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ292" s="61"/>
+      <c r="AK292" s="62">
+        <v>5.6</v>
+      </c>
+      <c r="AL292" s="62">
+        <v>3</v>
+      </c>
+      <c r="AM292" s="61"/>
+      <c r="AN292" s="61"/>
+      <c r="AO292" s="61"/>
+      <c r="AP292" s="61"/>
+      <c r="AQ292" s="61"/>
+      <c r="AR292" s="61"/>
+      <c r="AS292" s="61"/>
+      <c r="AT292" s="61"/>
+      <c r="AU292" s="63">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="293" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="62">
+        <v>58</v>
+      </c>
+      <c r="B293" s="63" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C293" s="63" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D293" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E293" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F293" s="61"/>
+      <c r="G293" s="61"/>
+      <c r="H293" s="63">
+        <v>786</v>
+      </c>
+      <c r="I293" s="63">
+        <v>69</v>
+      </c>
+      <c r="J293" s="63" t="s">
+        <v>880</v>
+      </c>
+      <c r="K293" s="62">
+        <v>2014</v>
+      </c>
+      <c r="L293" s="62">
+        <v>2014</v>
+      </c>
+      <c r="M293" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="N293" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O293" s="63" t="s">
+        <v>1009</v>
+      </c>
+      <c r="P293" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q293" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R293" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="S293" s="61"/>
+      <c r="T293" s="61"/>
+      <c r="U293" s="61"/>
+      <c r="V293" s="62">
+        <v>7.9</v>
+      </c>
+      <c r="W293" s="61"/>
+      <c r="X293" s="63">
+        <v>79.5</v>
+      </c>
+      <c r="Y293" s="64">
+        <v>41759</v>
+      </c>
+      <c r="Z293" s="61"/>
+      <c r="AA293" s="61"/>
+      <c r="AB293" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC293" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD293" s="62" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE293" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF293" s="63" t="s">
+        <v>997</v>
+      </c>
+      <c r="AG293" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH293" s="63" t="s">
+        <v>1010</v>
+      </c>
+      <c r="AI293" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ293" s="61"/>
+      <c r="AK293" s="62">
+        <v>6.5</v>
+      </c>
+      <c r="AL293" s="62">
+        <v>2.7</v>
+      </c>
+      <c r="AM293" s="61"/>
+      <c r="AN293" s="61"/>
+      <c r="AO293" s="61"/>
+      <c r="AP293" s="61"/>
+      <c r="AQ293" s="61"/>
+      <c r="AR293" s="61"/>
+      <c r="AS293" s="61"/>
+      <c r="AT293" s="61"/>
+      <c r="AU293" s="63">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="294" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="62">
+        <v>59</v>
+      </c>
+      <c r="B294" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C294" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D294" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E294" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F294" s="61"/>
+      <c r="G294" s="61"/>
+      <c r="H294" s="61"/>
+      <c r="I294" s="61"/>
+      <c r="J294" s="61"/>
+      <c r="K294" s="62">
+        <v>2012</v>
+      </c>
+      <c r="L294" s="62">
+        <v>2012</v>
+      </c>
+      <c r="M294" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N294" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O294" s="61"/>
+      <c r="P294" s="61"/>
+      <c r="Q294" s="61"/>
+      <c r="R294" s="61"/>
+      <c r="S294" s="61"/>
+      <c r="T294" s="61"/>
+      <c r="U294" s="61"/>
+      <c r="V294" s="61"/>
+      <c r="W294" s="61"/>
+      <c r="X294" s="61"/>
+      <c r="Y294" s="61"/>
+      <c r="Z294" s="61"/>
+      <c r="AA294" s="61"/>
+      <c r="AB294" s="61"/>
+      <c r="AC294" s="61"/>
+      <c r="AD294" s="62" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AE294" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF294" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG294" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH294" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI294" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ294" s="61"/>
+      <c r="AK294" s="61"/>
+      <c r="AL294" s="61"/>
+      <c r="AM294" s="61"/>
+      <c r="AN294" s="61"/>
+      <c r="AO294" s="61"/>
+      <c r="AP294" s="61"/>
+      <c r="AQ294" s="61"/>
+      <c r="AR294" s="61"/>
+      <c r="AS294" s="61"/>
+      <c r="AT294" s="61"/>
+      <c r="AU294" s="63">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A295" s="62">
+        <v>59</v>
+      </c>
+      <c r="B295" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C295" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D295" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E295" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F295" s="61"/>
+      <c r="G295" s="61"/>
+      <c r="H295" s="61"/>
+      <c r="I295" s="61"/>
+      <c r="J295" s="61"/>
+      <c r="K295" s="62">
+        <v>2012</v>
+      </c>
+      <c r="L295" s="62">
+        <v>2012</v>
+      </c>
+      <c r="M295" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N295" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O295" s="61"/>
+      <c r="P295" s="61"/>
+      <c r="Q295" s="61"/>
+      <c r="R295" s="61"/>
+      <c r="S295" s="61"/>
+      <c r="T295" s="61"/>
+      <c r="U295" s="61"/>
+      <c r="V295" s="61"/>
+      <c r="W295" s="61"/>
+      <c r="X295" s="61"/>
+      <c r="Y295" s="61"/>
+      <c r="Z295" s="61"/>
+      <c r="AA295" s="61"/>
+      <c r="AB295" s="61"/>
+      <c r="AC295" s="61"/>
+      <c r="AD295" s="62" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AE295" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF295" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG295" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH295" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI295" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ295" s="61"/>
+      <c r="AK295" s="61"/>
+      <c r="AL295" s="61"/>
+      <c r="AM295" s="61"/>
+      <c r="AN295" s="61"/>
+      <c r="AO295" s="61"/>
+      <c r="AP295" s="61"/>
+      <c r="AQ295" s="61"/>
+      <c r="AR295" s="61"/>
+      <c r="AS295" s="61"/>
+      <c r="AT295" s="61"/>
+      <c r="AU295" s="63">
+        <v>76.400000000000006</v>
+      </c>
+    </row>
+    <row r="296" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A296" s="62">
+        <v>59</v>
+      </c>
+      <c r="B296" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C296" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D296" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E296" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F296" s="61"/>
+      <c r="G296" s="61"/>
+      <c r="H296" s="61"/>
+      <c r="I296" s="61"/>
+      <c r="J296" s="61"/>
+      <c r="K296" s="62">
+        <v>2012</v>
+      </c>
+      <c r="L296" s="62">
+        <v>2012</v>
+      </c>
+      <c r="M296" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N296" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O296" s="61"/>
+      <c r="P296" s="61"/>
+      <c r="Q296" s="61"/>
+      <c r="R296" s="61"/>
+      <c r="S296" s="61"/>
+      <c r="T296" s="61"/>
+      <c r="U296" s="61"/>
+      <c r="V296" s="61"/>
+      <c r="W296" s="61"/>
+      <c r="X296" s="61"/>
+      <c r="Y296" s="61"/>
+      <c r="Z296" s="61"/>
+      <c r="AA296" s="61"/>
+      <c r="AB296" s="61"/>
+      <c r="AC296" s="61"/>
+      <c r="AD296" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE296" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF296" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG296" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH296" s="63" t="s">
+        <v>1016</v>
+      </c>
+      <c r="AI296" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ296" s="61"/>
+      <c r="AK296" s="61"/>
+      <c r="AL296" s="61"/>
+      <c r="AM296" s="61"/>
+      <c r="AN296" s="61"/>
+      <c r="AO296" s="61"/>
+      <c r="AP296" s="61"/>
+      <c r="AQ296" s="61"/>
+      <c r="AR296" s="61"/>
+      <c r="AS296" s="61"/>
+      <c r="AT296" s="61"/>
+      <c r="AU296" s="63">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="62">
+        <v>59</v>
+      </c>
+      <c r="B297" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C297" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D297" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E297" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F297" s="61"/>
+      <c r="G297" s="61"/>
+      <c r="H297" s="61"/>
+      <c r="I297" s="61"/>
+      <c r="J297" s="61"/>
+      <c r="K297" s="62">
+        <v>2012</v>
+      </c>
+      <c r="L297" s="62">
+        <v>2012</v>
+      </c>
+      <c r="M297" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N297" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O297" s="61"/>
+      <c r="P297" s="61"/>
+      <c r="Q297" s="61"/>
+      <c r="R297" s="61"/>
+      <c r="S297" s="61"/>
+      <c r="T297" s="61"/>
+      <c r="U297" s="61"/>
+      <c r="V297" s="61"/>
+      <c r="W297" s="61"/>
+      <c r="X297" s="61"/>
+      <c r="Y297" s="61"/>
+      <c r="Z297" s="61"/>
+      <c r="AA297" s="61"/>
+      <c r="AB297" s="61"/>
+      <c r="AC297" s="61"/>
+      <c r="AD297" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE297" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF297" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG297" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH297" s="63" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AI297" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ297" s="61"/>
+      <c r="AK297" s="61"/>
+      <c r="AL297" s="61"/>
+      <c r="AM297" s="61"/>
+      <c r="AN297" s="61"/>
+      <c r="AO297" s="61"/>
+      <c r="AP297" s="61"/>
+      <c r="AQ297" s="61"/>
+      <c r="AR297" s="61"/>
+      <c r="AS297" s="61"/>
+      <c r="AT297" s="61"/>
+      <c r="AU297" s="63">
+        <v>66.099999999999994</v>
+      </c>
+    </row>
+    <row r="298" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="62">
+        <v>59</v>
+      </c>
+      <c r="B298" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C298" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D298" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E298" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F298" s="61"/>
+      <c r="G298" s="61"/>
+      <c r="H298" s="61"/>
+      <c r="I298" s="61"/>
+      <c r="J298" s="61"/>
+      <c r="K298" s="62">
+        <v>2012</v>
+      </c>
+      <c r="L298" s="62">
+        <v>2012</v>
+      </c>
+      <c r="M298" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N298" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O298" s="61"/>
+      <c r="P298" s="61"/>
+      <c r="Q298" s="61"/>
+      <c r="R298" s="61"/>
+      <c r="S298" s="61"/>
+      <c r="T298" s="61"/>
+      <c r="U298" s="61"/>
+      <c r="V298" s="61"/>
+      <c r="W298" s="61"/>
+      <c r="X298" s="61"/>
+      <c r="Y298" s="61"/>
+      <c r="Z298" s="61"/>
+      <c r="AA298" s="61"/>
+      <c r="AB298" s="61"/>
+      <c r="AC298" s="61"/>
+      <c r="AD298" s="62" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AE298" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF298" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG298" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH298" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI298" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ298" s="61"/>
+      <c r="AK298" s="61"/>
+      <c r="AL298" s="61"/>
+      <c r="AM298" s="61"/>
+      <c r="AN298" s="61"/>
+      <c r="AO298" s="61"/>
+      <c r="AP298" s="61"/>
+      <c r="AQ298" s="61"/>
+      <c r="AR298" s="61"/>
+      <c r="AS298" s="61"/>
+      <c r="AT298" s="61"/>
+      <c r="AU298" s="63">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="299" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="62">
+        <v>59</v>
+      </c>
+      <c r="B299" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C299" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D299" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E299" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F299" s="61"/>
+      <c r="G299" s="61"/>
+      <c r="H299" s="61"/>
+      <c r="I299" s="61"/>
+      <c r="J299" s="61"/>
+      <c r="K299" s="62">
+        <v>2012</v>
+      </c>
+      <c r="L299" s="62">
+        <v>2012</v>
+      </c>
+      <c r="M299" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N299" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O299" s="61"/>
+      <c r="P299" s="61"/>
+      <c r="Q299" s="61"/>
+      <c r="R299" s="61"/>
+      <c r="S299" s="61"/>
+      <c r="T299" s="61"/>
+      <c r="U299" s="61"/>
+      <c r="V299" s="61"/>
+      <c r="W299" s="61"/>
+      <c r="X299" s="61"/>
+      <c r="Y299" s="61"/>
+      <c r="Z299" s="61"/>
+      <c r="AA299" s="61"/>
+      <c r="AB299" s="61"/>
+      <c r="AC299" s="61"/>
+      <c r="AD299" s="62" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AE299" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF299" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG299" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH299" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI299" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ299" s="61"/>
+      <c r="AK299" s="61"/>
+      <c r="AL299" s="61"/>
+      <c r="AM299" s="61"/>
+      <c r="AN299" s="61"/>
+      <c r="AO299" s="61"/>
+      <c r="AP299" s="61"/>
+      <c r="AQ299" s="61"/>
+      <c r="AR299" s="61"/>
+      <c r="AS299" s="61"/>
+      <c r="AT299" s="61"/>
+      <c r="AU299" s="63">
+        <v>68.900000000000006</v>
+      </c>
+    </row>
+    <row r="300" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="62">
+        <v>59</v>
+      </c>
+      <c r="B300" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C300" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D300" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E300" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F300" s="61"/>
+      <c r="G300" s="61"/>
+      <c r="H300" s="61"/>
+      <c r="I300" s="61"/>
+      <c r="J300" s="61"/>
+      <c r="K300" s="62">
+        <v>2012</v>
+      </c>
+      <c r="L300" s="62">
+        <v>2012</v>
+      </c>
+      <c r="M300" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N300" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O300" s="61"/>
+      <c r="P300" s="61"/>
+      <c r="Q300" s="61"/>
+      <c r="R300" s="61"/>
+      <c r="S300" s="61"/>
+      <c r="T300" s="61"/>
+      <c r="U300" s="61"/>
+      <c r="V300" s="61"/>
+      <c r="W300" s="61"/>
+      <c r="X300" s="61"/>
+      <c r="Y300" s="61"/>
+      <c r="Z300" s="61"/>
+      <c r="AA300" s="61"/>
+      <c r="AB300" s="61"/>
+      <c r="AC300" s="61"/>
+      <c r="AD300" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE300" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF300" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG300" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH300" s="63" t="s">
+        <v>1016</v>
+      </c>
+      <c r="AI300" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ300" s="61"/>
+      <c r="AK300" s="61"/>
+      <c r="AL300" s="61"/>
+      <c r="AM300" s="61"/>
+      <c r="AN300" s="61"/>
+      <c r="AO300" s="61"/>
+      <c r="AP300" s="61"/>
+      <c r="AQ300" s="61"/>
+      <c r="AR300" s="61"/>
+      <c r="AS300" s="61"/>
+      <c r="AT300" s="61"/>
+      <c r="AU300" s="63">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="301" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A301" s="62">
+        <v>59</v>
+      </c>
+      <c r="B301" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C301" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D301" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E301" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F301" s="61"/>
+      <c r="G301" s="61"/>
+      <c r="H301" s="61"/>
+      <c r="I301" s="61"/>
+      <c r="J301" s="61"/>
+      <c r="K301" s="62">
+        <v>2012</v>
+      </c>
+      <c r="L301" s="62">
+        <v>2012</v>
+      </c>
+      <c r="M301" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N301" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O301" s="61"/>
+      <c r="P301" s="61"/>
+      <c r="Q301" s="61"/>
+      <c r="R301" s="61"/>
+      <c r="S301" s="61"/>
+      <c r="T301" s="61"/>
+      <c r="U301" s="61"/>
+      <c r="V301" s="61"/>
+      <c r="W301" s="61"/>
+      <c r="X301" s="61"/>
+      <c r="Y301" s="61"/>
+      <c r="Z301" s="61"/>
+      <c r="AA301" s="61"/>
+      <c r="AB301" s="61"/>
+      <c r="AC301" s="61"/>
+      <c r="AD301" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE301" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF301" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG301" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH301" s="63" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AI301" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ301" s="61"/>
+      <c r="AK301" s="61"/>
+      <c r="AL301" s="61"/>
+      <c r="AM301" s="61"/>
+      <c r="AN301" s="61"/>
+      <c r="AO301" s="61"/>
+      <c r="AP301" s="61"/>
+      <c r="AQ301" s="61"/>
+      <c r="AR301" s="61"/>
+      <c r="AS301" s="61"/>
+      <c r="AT301" s="61"/>
+      <c r="AU301" s="63">
+        <v>83.1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="62">
+        <v>59</v>
+      </c>
+      <c r="B302" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C302" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D302" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E302" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F302" s="61"/>
+      <c r="G302" s="61"/>
+      <c r="H302" s="61"/>
+      <c r="I302" s="61"/>
+      <c r="J302" s="61"/>
+      <c r="K302" s="62">
+        <v>2013</v>
+      </c>
+      <c r="L302" s="62">
+        <v>2013</v>
+      </c>
+      <c r="M302" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N302" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O302" s="61"/>
+      <c r="P302" s="61"/>
+      <c r="Q302" s="61"/>
+      <c r="R302" s="61"/>
+      <c r="S302" s="61"/>
+      <c r="T302" s="61"/>
+      <c r="U302" s="61"/>
+      <c r="V302" s="61"/>
+      <c r="W302" s="61"/>
+      <c r="X302" s="61"/>
+      <c r="Y302" s="61"/>
+      <c r="Z302" s="61"/>
+      <c r="AA302" s="61"/>
+      <c r="AB302" s="61"/>
+      <c r="AC302" s="61"/>
+      <c r="AD302" s="62" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AE302" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF302" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG302" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH302" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI302" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ302" s="61"/>
+      <c r="AK302" s="61"/>
+      <c r="AL302" s="61"/>
+      <c r="AM302" s="61"/>
+      <c r="AN302" s="61"/>
+      <c r="AO302" s="61"/>
+      <c r="AP302" s="61"/>
+      <c r="AQ302" s="61"/>
+      <c r="AR302" s="61"/>
+      <c r="AS302" s="61"/>
+      <c r="AT302" s="61"/>
+      <c r="AU302" s="63">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="303" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="62">
+        <v>59</v>
+      </c>
+      <c r="B303" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C303" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D303" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E303" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F303" s="61"/>
+      <c r="G303" s="61"/>
+      <c r="H303" s="61"/>
+      <c r="I303" s="61"/>
+      <c r="J303" s="61"/>
+      <c r="K303" s="62">
+        <v>2013</v>
+      </c>
+      <c r="L303" s="62">
+        <v>2013</v>
+      </c>
+      <c r="M303" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N303" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O303" s="61"/>
+      <c r="P303" s="61"/>
+      <c r="Q303" s="61"/>
+      <c r="R303" s="61"/>
+      <c r="S303" s="61"/>
+      <c r="T303" s="61"/>
+      <c r="U303" s="61"/>
+      <c r="V303" s="61"/>
+      <c r="W303" s="61"/>
+      <c r="X303" s="61"/>
+      <c r="Y303" s="61"/>
+      <c r="Z303" s="61"/>
+      <c r="AA303" s="61"/>
+      <c r="AB303" s="61"/>
+      <c r="AC303" s="61"/>
+      <c r="AD303" s="62" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AE303" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF303" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG303" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH303" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI303" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ303" s="61"/>
+      <c r="AK303" s="61"/>
+      <c r="AL303" s="61"/>
+      <c r="AM303" s="61"/>
+      <c r="AN303" s="61"/>
+      <c r="AO303" s="61"/>
+      <c r="AP303" s="61"/>
+      <c r="AQ303" s="61"/>
+      <c r="AR303" s="61"/>
+      <c r="AS303" s="61"/>
+      <c r="AT303" s="61"/>
+      <c r="AU303" s="63">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="304" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="62">
+        <v>59</v>
+      </c>
+      <c r="B304" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C304" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D304" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E304" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F304" s="61"/>
+      <c r="G304" s="61"/>
+      <c r="H304" s="61"/>
+      <c r="I304" s="61"/>
+      <c r="J304" s="61"/>
+      <c r="K304" s="62">
+        <v>2013</v>
+      </c>
+      <c r="L304" s="62">
+        <v>2013</v>
+      </c>
+      <c r="M304" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N304" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O304" s="61"/>
+      <c r="P304" s="61"/>
+      <c r="Q304" s="61"/>
+      <c r="R304" s="61"/>
+      <c r="S304" s="61"/>
+      <c r="T304" s="61"/>
+      <c r="U304" s="61"/>
+      <c r="V304" s="61"/>
+      <c r="W304" s="61"/>
+      <c r="X304" s="61"/>
+      <c r="Y304" s="61"/>
+      <c r="Z304" s="61"/>
+      <c r="AA304" s="61"/>
+      <c r="AB304" s="61"/>
+      <c r="AC304" s="61"/>
+      <c r="AD304" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE304" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF304" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG304" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH304" s="63" t="s">
+        <v>1016</v>
+      </c>
+      <c r="AI304" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ304" s="61"/>
+      <c r="AK304" s="61"/>
+      <c r="AL304" s="61"/>
+      <c r="AM304" s="61"/>
+      <c r="AN304" s="61"/>
+      <c r="AO304" s="61"/>
+      <c r="AP304" s="61"/>
+      <c r="AQ304" s="61"/>
+      <c r="AR304" s="61"/>
+      <c r="AS304" s="61"/>
+      <c r="AT304" s="61"/>
+      <c r="AU304" s="63">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A305" s="62">
+        <v>59</v>
+      </c>
+      <c r="B305" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C305" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D305" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E305" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F305" s="61"/>
+      <c r="G305" s="61"/>
+      <c r="H305" s="61"/>
+      <c r="I305" s="61"/>
+      <c r="J305" s="61"/>
+      <c r="K305" s="62">
+        <v>2013</v>
+      </c>
+      <c r="L305" s="62">
+        <v>2013</v>
+      </c>
+      <c r="M305" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N305" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O305" s="61"/>
+      <c r="P305" s="61"/>
+      <c r="Q305" s="61"/>
+      <c r="R305" s="61"/>
+      <c r="S305" s="61"/>
+      <c r="T305" s="61"/>
+      <c r="U305" s="61"/>
+      <c r="V305" s="61"/>
+      <c r="W305" s="61"/>
+      <c r="X305" s="61"/>
+      <c r="Y305" s="61"/>
+      <c r="Z305" s="61"/>
+      <c r="AA305" s="61"/>
+      <c r="AB305" s="61"/>
+      <c r="AC305" s="61"/>
+      <c r="AD305" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE305" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF305" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG305" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH305" s="63" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AI305" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ305" s="61"/>
+      <c r="AK305" s="61"/>
+      <c r="AL305" s="61"/>
+      <c r="AM305" s="61"/>
+      <c r="AN305" s="61"/>
+      <c r="AO305" s="61"/>
+      <c r="AP305" s="61"/>
+      <c r="AQ305" s="61"/>
+      <c r="AR305" s="61"/>
+      <c r="AS305" s="61"/>
+      <c r="AT305" s="61"/>
+      <c r="AU305" s="63">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="306" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="62">
+        <v>59</v>
+      </c>
+      <c r="B306" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C306" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D306" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E306" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F306" s="61"/>
+      <c r="G306" s="61"/>
+      <c r="H306" s="61"/>
+      <c r="I306" s="61"/>
+      <c r="J306" s="61"/>
+      <c r="K306" s="62">
+        <v>2013</v>
+      </c>
+      <c r="L306" s="62">
+        <v>2013</v>
+      </c>
+      <c r="M306" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N306" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O306" s="61"/>
+      <c r="P306" s="61"/>
+      <c r="Q306" s="61"/>
+      <c r="R306" s="61"/>
+      <c r="S306" s="61"/>
+      <c r="T306" s="61"/>
+      <c r="U306" s="61"/>
+      <c r="V306" s="61"/>
+      <c r="W306" s="61"/>
+      <c r="X306" s="61"/>
+      <c r="Y306" s="61"/>
+      <c r="Z306" s="61"/>
+      <c r="AA306" s="61"/>
+      <c r="AB306" s="61"/>
+      <c r="AC306" s="61"/>
+      <c r="AD306" s="62" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AE306" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF306" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG306" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH306" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI306" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ306" s="61"/>
+      <c r="AK306" s="61"/>
+      <c r="AL306" s="61"/>
+      <c r="AM306" s="61"/>
+      <c r="AN306" s="61"/>
+      <c r="AO306" s="61"/>
+      <c r="AP306" s="61"/>
+      <c r="AQ306" s="61"/>
+      <c r="AR306" s="61"/>
+      <c r="AS306" s="61"/>
+      <c r="AT306" s="61"/>
+      <c r="AU306" s="63">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A307" s="62">
+        <v>59</v>
+      </c>
+      <c r="B307" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C307" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D307" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E307" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F307" s="61"/>
+      <c r="G307" s="61"/>
+      <c r="H307" s="61"/>
+      <c r="I307" s="61"/>
+      <c r="J307" s="61"/>
+      <c r="K307" s="62">
+        <v>2013</v>
+      </c>
+      <c r="L307" s="62">
+        <v>2013</v>
+      </c>
+      <c r="M307" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N307" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O307" s="61"/>
+      <c r="P307" s="61"/>
+      <c r="Q307" s="61"/>
+      <c r="R307" s="61"/>
+      <c r="S307" s="61"/>
+      <c r="T307" s="61"/>
+      <c r="U307" s="61"/>
+      <c r="V307" s="61"/>
+      <c r="W307" s="61"/>
+      <c r="X307" s="61"/>
+      <c r="Y307" s="61"/>
+      <c r="Z307" s="61"/>
+      <c r="AA307" s="61"/>
+      <c r="AB307" s="61"/>
+      <c r="AC307" s="61"/>
+      <c r="AD307" s="62" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AE307" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF307" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG307" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH307" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI307" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ307" s="61"/>
+      <c r="AK307" s="61"/>
+      <c r="AL307" s="61"/>
+      <c r="AM307" s="61"/>
+      <c r="AN307" s="61"/>
+      <c r="AO307" s="61"/>
+      <c r="AP307" s="61"/>
+      <c r="AQ307" s="61"/>
+      <c r="AR307" s="61"/>
+      <c r="AS307" s="61"/>
+      <c r="AT307" s="61"/>
+      <c r="AU307" s="63">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="62">
+        <v>59</v>
+      </c>
+      <c r="B308" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C308" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D308" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E308" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F308" s="61"/>
+      <c r="G308" s="61"/>
+      <c r="H308" s="61"/>
+      <c r="I308" s="61"/>
+      <c r="J308" s="61"/>
+      <c r="K308" s="62">
+        <v>2013</v>
+      </c>
+      <c r="L308" s="62">
+        <v>2013</v>
+      </c>
+      <c r="M308" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N308" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O308" s="61"/>
+      <c r="P308" s="61"/>
+      <c r="Q308" s="61"/>
+      <c r="R308" s="61"/>
+      <c r="S308" s="61"/>
+      <c r="T308" s="61"/>
+      <c r="U308" s="61"/>
+      <c r="V308" s="61"/>
+      <c r="W308" s="61"/>
+      <c r="X308" s="61"/>
+      <c r="Y308" s="61"/>
+      <c r="Z308" s="61"/>
+      <c r="AA308" s="61"/>
+      <c r="AB308" s="61"/>
+      <c r="AC308" s="61"/>
+      <c r="AD308" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE308" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF308" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG308" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH308" s="63" t="s">
+        <v>1016</v>
+      </c>
+      <c r="AI308" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ308" s="61"/>
+      <c r="AK308" s="61"/>
+      <c r="AL308" s="61"/>
+      <c r="AM308" s="61"/>
+      <c r="AN308" s="61"/>
+      <c r="AO308" s="61"/>
+      <c r="AP308" s="61"/>
+      <c r="AQ308" s="61"/>
+      <c r="AR308" s="61"/>
+      <c r="AS308" s="61"/>
+      <c r="AT308" s="61"/>
+      <c r="AU308" s="63">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="62">
+        <v>59</v>
+      </c>
+      <c r="B309" s="63" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C309" s="63" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D309" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E309" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F309" s="61"/>
+      <c r="G309" s="61"/>
+      <c r="H309" s="61"/>
+      <c r="I309" s="61"/>
+      <c r="J309" s="61"/>
+      <c r="K309" s="62">
+        <v>2013</v>
+      </c>
+      <c r="L309" s="62">
+        <v>2013</v>
+      </c>
+      <c r="M309" s="63" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N309" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O309" s="61"/>
+      <c r="P309" s="61"/>
+      <c r="Q309" s="61"/>
+      <c r="R309" s="61"/>
+      <c r="S309" s="61"/>
+      <c r="T309" s="61"/>
+      <c r="U309" s="61"/>
+      <c r="V309" s="61"/>
+      <c r="W309" s="61"/>
+      <c r="X309" s="61"/>
+      <c r="Y309" s="61"/>
+      <c r="Z309" s="61"/>
+      <c r="AA309" s="61"/>
+      <c r="AB309" s="61"/>
+      <c r="AC309" s="61"/>
+      <c r="AD309" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE309" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF309" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG309" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH309" s="63" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AI309" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ309" s="61"/>
+      <c r="AK309" s="61"/>
+      <c r="AL309" s="61"/>
+      <c r="AM309" s="61"/>
+      <c r="AN309" s="61"/>
+      <c r="AO309" s="61"/>
+      <c r="AP309" s="61"/>
+      <c r="AQ309" s="61"/>
+      <c r="AR309" s="61"/>
+      <c r="AS309" s="61"/>
+      <c r="AT309" s="61"/>
+      <c r="AU309" s="63">
+        <v>77.2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A310" s="62">
+        <v>60</v>
+      </c>
+      <c r="B310" s="63" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C310" s="63" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D310" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E310" s="65" t="s">
+        <v>875</v>
+      </c>
+      <c r="F310" s="61"/>
+      <c r="G310" s="61"/>
+      <c r="H310" s="61"/>
+      <c r="I310" s="61"/>
+      <c r="J310" s="61"/>
+      <c r="K310" s="62">
+        <v>2001</v>
+      </c>
+      <c r="L310" s="62">
+        <v>2003</v>
+      </c>
+      <c r="M310" s="63" t="s">
+        <v>1020</v>
+      </c>
+      <c r="N310" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O310" s="63" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P310" s="63" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q310" s="62" t="s">
+        <v>1021</v>
+      </c>
+      <c r="R310" s="62">
+        <v>4.2</v>
+      </c>
+      <c r="S310" s="61"/>
+      <c r="T310" s="62">
+        <v>3.1</v>
+      </c>
+      <c r="U310" s="61"/>
+      <c r="V310" s="62">
+        <v>6.3</v>
+      </c>
+      <c r="W310" s="63">
+        <v>30.7</v>
+      </c>
+      <c r="X310" s="63">
+        <v>94</v>
+      </c>
+      <c r="Y310" s="61"/>
+      <c r="Z310" s="61"/>
+      <c r="AA310" s="61"/>
+      <c r="AB310" s="63" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AC310" s="61"/>
+      <c r="AD310" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE310" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF310" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="AG310" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH310" s="63" t="s">
+        <v>998</v>
+      </c>
+      <c r="AI310" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ310" s="61"/>
+      <c r="AK310" s="61"/>
+      <c r="AL310" s="61"/>
+      <c r="AM310" s="62">
+        <v>49</v>
+      </c>
+      <c r="AN310" s="61"/>
+      <c r="AO310" s="61"/>
+      <c r="AP310" s="62">
+        <v>16</v>
+      </c>
+      <c r="AQ310" s="61"/>
+      <c r="AR310" s="61"/>
+      <c r="AS310" s="61"/>
+      <c r="AT310" s="61"/>
+      <c r="AU310" s="63">
+        <v>67.34693877551021</v>
+      </c>
+    </row>
+    <row r="311" spans="1:47" ht="150.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="62">
+        <v>61</v>
+      </c>
+      <c r="B311" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C311" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D311" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E311" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F311" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G311" s="61"/>
+      <c r="H311" s="63">
+        <v>140</v>
+      </c>
+      <c r="I311" s="63">
+        <v>430</v>
+      </c>
+      <c r="J311" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K311" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L311" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M311" s="63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N311" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O311" s="63" t="s">
+        <v>1028</v>
+      </c>
+      <c r="P311" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q311" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R311" s="62">
+        <v>4.8</v>
+      </c>
+      <c r="S311" s="61"/>
+      <c r="T311" s="62">
+        <v>1.8</v>
+      </c>
+      <c r="U311" s="61"/>
+      <c r="V311" s="62">
+        <v>7.1</v>
+      </c>
+      <c r="W311" s="61"/>
+      <c r="X311" s="63">
+        <v>64</v>
+      </c>
+      <c r="Y311" s="61"/>
+      <c r="Z311" s="61"/>
+      <c r="AA311" s="61"/>
+      <c r="AB311" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC311" s="61"/>
+      <c r="AD311" s="62" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AE311" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF311" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG311" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH311" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AI311" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ311" s="61"/>
+      <c r="AK311" s="62">
+        <v>6</v>
+      </c>
+      <c r="AL311" s="61"/>
+      <c r="AM311" s="62">
+        <v>17</v>
+      </c>
+      <c r="AN311" s="61"/>
+      <c r="AO311" s="61"/>
+      <c r="AP311" s="62">
+        <v>2.5</v>
+      </c>
+      <c r="AQ311" s="61"/>
+      <c r="AR311" s="61"/>
+      <c r="AS311" s="61"/>
+      <c r="AT311" s="61"/>
+      <c r="AU311" s="63">
+        <v>85.294117647058826</v>
+      </c>
+    </row>
+    <row r="312" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A312" s="62">
+        <v>61</v>
+      </c>
+      <c r="B312" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C312" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D312" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E312" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F312" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G312" s="61"/>
+      <c r="H312" s="63">
+        <v>140</v>
+      </c>
+      <c r="I312" s="63">
+        <v>430</v>
+      </c>
+      <c r="J312" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K312" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L312" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M312" s="63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N312" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O312" s="63" t="s">
+        <v>1028</v>
+      </c>
+      <c r="P312" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q312" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R312" s="62">
+        <v>4.8</v>
+      </c>
+      <c r="S312" s="61"/>
+      <c r="T312" s="62">
+        <v>1.8</v>
+      </c>
+      <c r="U312" s="61"/>
+      <c r="V312" s="62">
+        <v>7.1</v>
+      </c>
+      <c r="W312" s="61"/>
+      <c r="X312" s="63">
+        <v>64</v>
+      </c>
+      <c r="Y312" s="61"/>
+      <c r="Z312" s="61"/>
+      <c r="AA312" s="61"/>
+      <c r="AB312" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC312" s="61"/>
+      <c r="AD312" s="62" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AE312" s="62" t="s">
+        <v>940</v>
+      </c>
+      <c r="AF312" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG312" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH312" s="61"/>
+      <c r="AI312" s="61"/>
+      <c r="AJ312" s="61"/>
+      <c r="AK312" s="61"/>
+      <c r="AL312" s="61"/>
+      <c r="AM312" s="62">
+        <v>17</v>
+      </c>
+      <c r="AN312" s="61"/>
+      <c r="AO312" s="61"/>
+      <c r="AP312" s="62">
+        <v>13.5</v>
+      </c>
+      <c r="AQ312" s="61"/>
+      <c r="AR312" s="61"/>
+      <c r="AS312" s="61"/>
+      <c r="AT312" s="61"/>
+      <c r="AU312" s="63">
+        <v>20.588235294117649</v>
+      </c>
+    </row>
+    <row r="313" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A313" s="62">
+        <v>61</v>
+      </c>
+      <c r="B313" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C313" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D313" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E313" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F313" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G313" s="61"/>
+      <c r="H313" s="63">
+        <v>140</v>
+      </c>
+      <c r="I313" s="63">
+        <v>430</v>
+      </c>
+      <c r="J313" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K313" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L313" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M313" s="63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N313" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O313" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P313" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q313" s="62" t="s">
+        <v>1021</v>
+      </c>
+      <c r="R313" s="62">
+        <v>9.5</v>
+      </c>
+      <c r="S313" s="61"/>
+      <c r="T313" s="62">
+        <v>1.9</v>
+      </c>
+      <c r="U313" s="61"/>
+      <c r="V313" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="W313" s="61"/>
+      <c r="X313" s="63">
+        <v>65</v>
+      </c>
+      <c r="Y313" s="61"/>
+      <c r="Z313" s="61"/>
+      <c r="AA313" s="61"/>
+      <c r="AB313" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC313" s="61"/>
+      <c r="AD313" s="62" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AE313" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF313" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG313" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH313" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AI313" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ313" s="61"/>
+      <c r="AK313" s="62">
+        <v>6</v>
+      </c>
+      <c r="AL313" s="61"/>
+      <c r="AM313" s="62">
+        <v>26</v>
+      </c>
+      <c r="AN313" s="61"/>
+      <c r="AO313" s="61"/>
+      <c r="AP313" s="62">
+        <v>6.5</v>
+      </c>
+      <c r="AQ313" s="61"/>
+      <c r="AR313" s="61"/>
+      <c r="AS313" s="61"/>
+      <c r="AT313" s="61"/>
+      <c r="AU313" s="63">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="314" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A314" s="62">
+        <v>61</v>
+      </c>
+      <c r="B314" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C314" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D314" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E314" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F314" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G314" s="61"/>
+      <c r="H314" s="63">
+        <v>140</v>
+      </c>
+      <c r="I314" s="63">
+        <v>430</v>
+      </c>
+      <c r="J314" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K314" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L314" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M314" s="63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N314" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O314" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="P314" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q314" s="62" t="s">
+        <v>1021</v>
+      </c>
+      <c r="R314" s="62">
+        <v>10.5</v>
+      </c>
+      <c r="S314" s="61"/>
+      <c r="T314" s="62">
+        <v>1.9</v>
+      </c>
+      <c r="U314" s="61"/>
+      <c r="V314" s="62">
+        <v>6.8</v>
+      </c>
+      <c r="W314" s="61"/>
+      <c r="X314" s="63">
+        <v>65</v>
+      </c>
+      <c r="Y314" s="61"/>
+      <c r="Z314" s="61"/>
+      <c r="AA314" s="61"/>
+      <c r="AB314" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC314" s="61"/>
+      <c r="AD314" s="62" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AE314" s="62" t="s">
+        <v>940</v>
+      </c>
+      <c r="AF314" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG314" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH314" s="61"/>
+      <c r="AI314" s="61"/>
+      <c r="AJ314" s="61"/>
+      <c r="AK314" s="61"/>
+      <c r="AL314" s="61"/>
+      <c r="AM314" s="62">
+        <v>26</v>
+      </c>
+      <c r="AN314" s="61"/>
+      <c r="AO314" s="61"/>
+      <c r="AP314" s="62">
+        <v>18</v>
+      </c>
+      <c r="AQ314" s="61"/>
+      <c r="AR314" s="61"/>
+      <c r="AS314" s="61"/>
+      <c r="AT314" s="61"/>
+      <c r="AU314" s="63">
+        <v>30.76923076923077</v>
+      </c>
+    </row>
+    <row r="315" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A315" s="62">
+        <v>61</v>
+      </c>
+      <c r="B315" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C315" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D315" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E315" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F315" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G315" s="61"/>
+      <c r="H315" s="63">
+        <v>140</v>
+      </c>
+      <c r="I315" s="63">
+        <v>430</v>
+      </c>
+      <c r="J315" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K315" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L315" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M315" s="63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N315" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O315" s="63" t="s">
+        <v>494</v>
+      </c>
+      <c r="P315" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q315" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R315" s="62">
+        <v>3.9</v>
+      </c>
+      <c r="S315" s="61"/>
+      <c r="T315" s="62">
+        <v>3.2</v>
+      </c>
+      <c r="U315" s="61"/>
+      <c r="V315" s="62">
+        <v>7.6</v>
+      </c>
+      <c r="W315" s="61"/>
+      <c r="X315" s="63">
+        <v>56</v>
+      </c>
+      <c r="Y315" s="61"/>
+      <c r="Z315" s="61"/>
+      <c r="AA315" s="61"/>
+      <c r="AB315" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC315" s="61"/>
+      <c r="AD315" s="62" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AE315" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF315" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG315" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH315" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AI315" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="AJ315" s="61"/>
+      <c r="AK315" s="62">
+        <v>6.7</v>
+      </c>
+      <c r="AL315" s="61"/>
+      <c r="AM315" s="62">
+        <v>17.8</v>
+      </c>
+      <c r="AN315" s="61"/>
+      <c r="AO315" s="61"/>
+      <c r="AP315" s="62">
+        <v>2.8</v>
+      </c>
+      <c r="AQ315" s="61"/>
+      <c r="AR315" s="61"/>
+      <c r="AS315" s="61"/>
+      <c r="AT315" s="61"/>
+      <c r="AU315" s="63">
+        <v>84.269662921348313</v>
+      </c>
+    </row>
+    <row r="316" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A316" s="62">
+        <v>61</v>
+      </c>
+      <c r="B316" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C316" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D316" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E316" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F316" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G316" s="61"/>
+      <c r="H316" s="63">
+        <v>140</v>
+      </c>
+      <c r="I316" s="63">
+        <v>430</v>
+      </c>
+      <c r="J316" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K316" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L316" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M316" s="63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N316" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O316" s="63" t="s">
+        <v>494</v>
+      </c>
+      <c r="P316" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q316" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R316" s="62">
+        <v>3.9</v>
+      </c>
+      <c r="S316" s="61"/>
+      <c r="T316" s="62">
+        <v>3.2</v>
+      </c>
+      <c r="U316" s="61"/>
+      <c r="V316" s="62">
+        <v>7.6</v>
+      </c>
+      <c r="W316" s="61"/>
+      <c r="X316" s="63">
+        <v>56</v>
+      </c>
+      <c r="Y316" s="61"/>
+      <c r="Z316" s="61"/>
+      <c r="AA316" s="61"/>
+      <c r="AB316" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC316" s="61"/>
+      <c r="AD316" s="62" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AE316" s="62" t="s">
+        <v>940</v>
+      </c>
+      <c r="AF316" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG316" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH316" s="61"/>
+      <c r="AI316" s="61"/>
+      <c r="AJ316" s="61"/>
+      <c r="AK316" s="61"/>
+      <c r="AL316" s="61"/>
+      <c r="AM316" s="62">
+        <v>17.8</v>
+      </c>
+      <c r="AN316" s="61"/>
+      <c r="AO316" s="61"/>
+      <c r="AP316" s="62">
+        <v>16</v>
+      </c>
+      <c r="AQ316" s="61"/>
+      <c r="AR316" s="61"/>
+      <c r="AS316" s="61"/>
+      <c r="AT316" s="61"/>
+      <c r="AU316" s="63">
+        <v>10.1123595505618</v>
+      </c>
+    </row>
+    <row r="317" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A317" s="62">
+        <v>61</v>
+      </c>
+      <c r="B317" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C317" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D317" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E317" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F317" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G317" s="61"/>
+      <c r="H317" s="63">
+        <v>140</v>
+      </c>
+      <c r="I317" s="63">
+        <v>430</v>
+      </c>
+      <c r="J317" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K317" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L317" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M317" s="63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N317" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O317" s="63" t="s">
+        <v>352</v>
+      </c>
+      <c r="P317" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q317" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R317" s="62">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S317" s="61"/>
+      <c r="T317" s="62">
+        <v>2</v>
+      </c>
+      <c r="U317" s="61"/>
+      <c r="V317" s="62">
+        <v>7.1</v>
+      </c>
+      <c r="W317" s="61"/>
+      <c r="X317" s="63">
+        <v>71</v>
+      </c>
+      <c r="Y317" s="61"/>
+      <c r="Z317" s="61"/>
+      <c r="AA317" s="61"/>
+      <c r="AB317" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC317" s="61"/>
+      <c r="AD317" s="62" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AE317" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF317" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG317" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH317" s="63" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AI317" s="63" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AJ317" s="61"/>
+      <c r="AK317" s="61"/>
+      <c r="AL317" s="61"/>
+      <c r="AM317" s="62">
+        <v>29</v>
+      </c>
+      <c r="AN317" s="61"/>
+      <c r="AO317" s="61"/>
+      <c r="AP317" s="62">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="AQ317" s="61"/>
+      <c r="AR317" s="61"/>
+      <c r="AS317" s="61"/>
+      <c r="AT317" s="61"/>
+      <c r="AU317" s="63">
+        <v>-11.034482758620699</v>
+      </c>
+    </row>
+    <row r="318" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A318" s="62">
+        <v>61</v>
+      </c>
+      <c r="B318" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C318" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D318" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E318" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F318" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G318" s="61"/>
+      <c r="H318" s="63">
+        <v>140</v>
+      </c>
+      <c r="I318" s="63">
+        <v>430</v>
+      </c>
+      <c r="J318" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K318" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L318" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M318" s="63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N318" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="O318" s="63" t="s">
+        <v>352</v>
+      </c>
+      <c r="P318" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q318" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R318" s="62">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S318" s="61"/>
+      <c r="T318" s="62">
+        <v>3.4</v>
+      </c>
+      <c r="U318" s="61"/>
+      <c r="V318" s="62">
+        <v>7.8</v>
+      </c>
+      <c r="W318" s="61"/>
+      <c r="X318" s="63">
+        <v>60</v>
+      </c>
+      <c r="Y318" s="61"/>
+      <c r="Z318" s="61"/>
+      <c r="AA318" s="61"/>
+      <c r="AB318" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC318" s="61"/>
+      <c r="AD318" s="62" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AE318" s="62" t="s">
+        <v>936</v>
+      </c>
+      <c r="AF318" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG318" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH318" s="63" t="s">
+        <v>539</v>
+      </c>
+      <c r="AI318" s="63" t="s">
+        <v>954</v>
+      </c>
+      <c r="AJ318" s="61"/>
+      <c r="AK318" s="61"/>
+      <c r="AL318" s="61"/>
+      <c r="AM318" s="62">
+        <v>29</v>
+      </c>
+      <c r="AN318" s="61"/>
+      <c r="AO318" s="61"/>
+      <c r="AP318" s="62">
+        <v>23.5</v>
+      </c>
+      <c r="AQ318" s="61"/>
+      <c r="AR318" s="61"/>
+      <c r="AS318" s="61"/>
+      <c r="AT318" s="61"/>
+      <c r="AU318" s="63">
+        <v>18.96551724137931</v>
+      </c>
+    </row>
+    <row r="319" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A319" s="62">
+        <v>61</v>
+      </c>
+      <c r="B319" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C319" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D319" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E319" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F319" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G319" s="61"/>
+      <c r="H319" s="63">
+        <v>140</v>
+      </c>
+      <c r="I319" s="63">
+        <v>430</v>
+      </c>
+      <c r="J319" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K319" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L319" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M319" s="63" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N319" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O319" s="63" t="s">
+        <v>1033</v>
+      </c>
+      <c r="P319" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q319" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R319" s="62">
+        <v>4.5</v>
+      </c>
+      <c r="S319" s="61"/>
+      <c r="T319" s="62">
+        <v>2</v>
+      </c>
+      <c r="U319" s="61"/>
+      <c r="V319" s="62">
+        <v>7.1</v>
+      </c>
+      <c r="W319" s="61"/>
+      <c r="X319" s="63">
+        <v>72</v>
+      </c>
+      <c r="Y319" s="61"/>
+      <c r="Z319" s="61"/>
+      <c r="AA319" s="61"/>
+      <c r="AB319" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC319" s="61"/>
+      <c r="AD319" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AE319" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF319" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG319" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH319" s="61"/>
+      <c r="AI319" s="61"/>
+      <c r="AJ319" s="61"/>
+      <c r="AK319" s="61"/>
+      <c r="AL319" s="61"/>
+      <c r="AM319" s="62">
+        <v>22.8</v>
+      </c>
+      <c r="AN319" s="61"/>
+      <c r="AO319" s="61"/>
+      <c r="AP319" s="62">
+        <v>22.2</v>
+      </c>
+      <c r="AQ319" s="61"/>
+      <c r="AR319" s="61"/>
+      <c r="AS319" s="61"/>
+      <c r="AT319" s="61"/>
+      <c r="AU319" s="63">
+        <v>2.631578947368427</v>
+      </c>
+    </row>
+    <row r="320" spans="1:47" ht="150" x14ac:dyDescent="0.25">
+      <c r="A320" s="62">
+        <v>61</v>
+      </c>
+      <c r="B320" s="63" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C320" s="63" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D320" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E320" s="63" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F320" s="63" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G320" s="61"/>
+      <c r="H320" s="63">
+        <v>140</v>
+      </c>
+      <c r="I320" s="63">
+        <v>430</v>
+      </c>
+      <c r="J320" s="63" t="s">
+        <v>882</v>
+      </c>
+      <c r="K320" s="62">
+        <v>2019</v>
+      </c>
+      <c r="L320" s="62">
+        <v>2019</v>
+      </c>
+      <c r="M320" s="63" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N320" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="O320" s="63" t="s">
+        <v>1033</v>
+      </c>
+      <c r="P320" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q320" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="R320" s="62">
+        <v>4.5</v>
+      </c>
+      <c r="S320" s="61"/>
+      <c r="T320" s="62">
+        <v>2</v>
+      </c>
+      <c r="U320" s="61"/>
+      <c r="V320" s="62">
+        <v>7.1</v>
+      </c>
+      <c r="W320" s="61"/>
+      <c r="X320" s="63">
+        <v>72</v>
+      </c>
+      <c r="Y320" s="61"/>
+      <c r="Z320" s="61"/>
+      <c r="AA320" s="61"/>
+      <c r="AB320" s="63" t="s">
+        <v>986</v>
+      </c>
+      <c r="AC320" s="61"/>
+      <c r="AD320" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AE320" s="62" t="s">
+        <v>933</v>
+      </c>
+      <c r="AF320" s="63" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG320" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="AH320" s="61"/>
+      <c r="AI320" s="61"/>
+      <c r="AJ320" s="61"/>
+      <c r="AK320" s="61"/>
+      <c r="AL320" s="61"/>
+      <c r="AM320" s="62">
+        <v>22.8</v>
+      </c>
+      <c r="AN320" s="61"/>
+      <c r="AO320" s="61"/>
+      <c r="AP320" s="62">
+        <v>14.6</v>
+      </c>
+      <c r="AQ320" s="61"/>
+      <c r="AR320" s="61"/>
+      <c r="AS320" s="61"/>
+      <c r="AT320" s="61"/>
+      <c r="AU320" s="63">
+        <v>35.96491228070176</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AY273" xr:uid="{9D35D03E-84A5-4E70-9EFA-07826CEBC622}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reductions/data/lit_dat.xlsx
+++ b/reductions/data/lit_dat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEC0645A-5384-4BE0-801A-F2F6905BE802}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D484913B-73F5-43B3-A6A4-9D9DF7B62CB7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{DF353E34-80BC-440D-84E6-1A1BEACE8767}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Database to use" sheetId="15" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Database to use'!$A$1:$AY$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Database to use'!$A$1:$AY$321</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -301,7 +301,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9796" uniqueCount="1037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9898" uniqueCount="1054">
   <si>
     <t>Study</t>
   </si>
@@ -3614,6 +3614,57 @@
   <si>
     <t>open slot injection and trailing shoe</t>
   </si>
+  <si>
+    <t>Bhandral et al., 2009</t>
+  </si>
+  <si>
+    <t>Bittmann et al., 2005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bittman, S., van Vliet, L. J. P., Kowalenko, C. G., McGinn, S., Hunt, D. E., &amp; Bounaix, F. (2005). Surface‐Banding Liquid Manure over Aeration Slots: A New Low‐Disturbance Method for Reducing Ammonia Emissions and Improving Yield of Perennial Grasses. Agronomy Journal, 97(5), 1304-1313. https://doi.org/10.2134/agronj2004.0277 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0287 </t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0288</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0289</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0290</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0291</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0292</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0293</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0294</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0295</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0296</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0297</t>
+  </si>
+  <si>
+    <t>Bhandral, R., Bittman, S., Kowalenko, G., Buckley, K., Chantigny, M. H., Hunt, D. E., Bounaix, F., &amp; Friesen, A. (2009). Enhancing soil infiltration reduces gaseous emissions and improves N uptake from applied dairy slurry. Journal of Environmental Quality, 38(4), 1372-1382. https://doi.org/10.2134/jeq2008.0298</t>
+  </si>
+  <si>
+    <t>The micro met measurements</t>
+  </si>
 </sst>
 </file>
 
@@ -3622,7 +3673,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3670,6 +3721,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4748,7 +4805,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D35D03E-84A5-4E70-9EFA-07826CEBC622}">
-  <dimension ref="A1:AY320"/>
+  <dimension ref="A1:AY336"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" style="1"/>
@@ -25674,7 +25731,7 @@
         <v>101</v>
       </c>
       <c r="AM149" s="1">
-        <v>52.7</v>
+        <v>41</v>
       </c>
       <c r="AN149" s="1" t="s">
         <v>101</v>
@@ -25696,7 +25753,7 @@
       </c>
       <c r="AT149" s="2">
         <f t="shared" si="41"/>
-        <v>88.614800759013278</v>
+        <v>85.365853658536579</v>
       </c>
       <c r="AU149" s="47">
         <v>88.614800759013278</v>
@@ -48266,8 +48323,539 @@
         <v>35.96491228070176</v>
       </c>
     </row>
+    <row r="321" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A321" s="1">
+        <v>62</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P321" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q321" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE321" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG321" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM321" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="AP321" s="1">
+        <v>24.6</v>
+      </c>
+      <c r="AU321" s="2">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A322" s="1">
+        <v>62</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P322" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q322" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE322" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG322" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM322" s="1">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="AP322" s="1">
+        <v>14.9</v>
+      </c>
+      <c r="AU322" s="2">
+        <v>61.989795918367349</v>
+      </c>
+    </row>
+    <row r="323" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A323" s="1">
+        <v>62</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P323" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q323" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE323" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG323" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM323" s="1">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="AP323" s="1">
+        <v>24.1</v>
+      </c>
+      <c r="AU323" s="2">
+        <v>38.676844783715005</v>
+      </c>
+    </row>
+    <row r="324" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A324" s="1">
+        <v>62</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P324" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q324" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE324" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG324" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM324" s="1">
+        <v>38</v>
+      </c>
+      <c r="AP324" s="1">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AU324" s="2">
+        <v>52.89473684210526</v>
+      </c>
+    </row>
+    <row r="325" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A325" s="1">
+        <v>62</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P325" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q325" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE325" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG325" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM325" s="1">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="AP325" s="1">
+        <v>25.1</v>
+      </c>
+      <c r="AU325" s="2">
+        <v>31.607629427792915</v>
+      </c>
+    </row>
+    <row r="326" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A326" s="1">
+        <v>62</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P326" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q326" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE326" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG326" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM326" s="1">
+        <v>51</v>
+      </c>
+      <c r="AP326" s="1">
+        <v>28.2</v>
+      </c>
+      <c r="AU326" s="2">
+        <v>44.705882352941174</v>
+      </c>
+    </row>
+    <row r="327" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A327" s="1">
+        <v>62</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P327" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q327" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE327" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG327" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM327" s="1">
+        <v>37.4</v>
+      </c>
+      <c r="AP327" s="1">
+        <v>23.5</v>
+      </c>
+      <c r="AU327" s="2">
+        <v>37.16577540106951</v>
+      </c>
+    </row>
+    <row r="328" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A328" s="1">
+        <v>62</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P328" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q328" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE328" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG328" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM328" s="1">
+        <v>39.1</v>
+      </c>
+      <c r="AP328" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="AU328" s="2">
+        <v>26.854219948849099</v>
+      </c>
+    </row>
+    <row r="329" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A329" s="1">
+        <v>62</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P329" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q329" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE329" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG329" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM329" s="1">
+        <v>39.1</v>
+      </c>
+      <c r="AP329" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="AU329" s="2">
+        <v>35.038363171355499</v>
+      </c>
+    </row>
+    <row r="330" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A330" s="1">
+        <v>62</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P330" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q330" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE330" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG330" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM330" s="1">
+        <v>16.3</v>
+      </c>
+      <c r="AP330" s="1">
+        <v>10</v>
+      </c>
+      <c r="AU330" s="2">
+        <v>38.650306748466257</v>
+      </c>
+    </row>
+    <row r="331" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A331" s="1">
+        <v>62</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P331" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q331" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE331" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG331" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM331" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="AP331" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="AU331" s="2">
+        <v>64.916467780429585</v>
+      </c>
+    </row>
+    <row r="332" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A332" s="1">
+        <v>62</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P332" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q332" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE332" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG332" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM332" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="AP332" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="AU332" s="2">
+        <v>67.910447761194035</v>
+      </c>
+    </row>
+    <row r="333" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A333" s="1">
+        <v>63</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AE333" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AG333" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="AM333" s="1">
+        <v>45.1</v>
+      </c>
+      <c r="AP333" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="AU333" s="2">
+        <v>57.206208425720618</v>
+      </c>
+      <c r="AY333" s="1" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="334" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A334" s="1">
+        <v>63</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AM334" s="1">
+        <v>24.1</v>
+      </c>
+      <c r="AP334" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="AU334" s="2">
+        <v>38.589211618257259</v>
+      </c>
+      <c r="AY334" s="1" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="335" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A335" s="1">
+        <v>63</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AM335" s="1">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AP335" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="AU335" s="2">
+        <v>43.121693121693113</v>
+      </c>
+      <c r="AY335" s="1" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="336" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A336" s="1">
+        <v>63</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AM336" s="1">
+        <v>21.2</v>
+      </c>
+      <c r="AP336" s="1">
+        <v>14</v>
+      </c>
+      <c r="AU336" s="2">
+        <v>33.96226415094339</v>
+      </c>
+      <c r="AY336" s="1" t="s">
+        <v>1053</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AY273" xr:uid="{9D35D03E-84A5-4E70-9EFA-07826CEBC622}"/>
+  <autoFilter ref="A1:AY321" xr:uid="{9D35D03E-84A5-4E70-9EFA-07826CEBC622}"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Calibri"&amp;10&amp;K000000 Unclassified / Non classifié&amp;1#_x000D_</oddHeader>

--- a/reductions/data/lit_dat.xlsx
+++ b/reductions/data/lit_dat.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="219" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D484913B-73F5-43B3-A6A4-9D9DF7B62CB7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{DF353E34-80BC-440D-84E6-1A1BEACE8767}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{DF353E34-80BC-440D-84E6-1A1BEACE8767}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable explanation" sheetId="2" r:id="rId1"/>
@@ -4458,14 +4458,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7CE9C9-127E-4846-B34D-8BA0CB6E1A90}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" customWidth="1"/>
-    <col min="3" max="3" width="137.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="137.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -4806,53 +4806,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D35D03E-84A5-4E70-9EFA-07826CEBC622}">
   <dimension ref="A1:AY336"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="1"/>
-    <col min="2" max="2" width="14.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="59.81640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="6.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.453125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="19.453125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="14.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="59.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="2" customWidth="1"/>
+    <col min="9" max="10" width="19.42578125" style="2" customWidth="1"/>
     <col min="11" max="11" width="11" style="5" customWidth="1"/>
-    <col min="12" max="12" width="12.453125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="5" customWidth="1"/>
     <col min="13" max="14" width="23" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.453125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="15.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="11.1796875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.54296875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.54296875" style="2" customWidth="1"/>
-    <col min="27" max="28" width="9.453125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="20.453125" style="2" customWidth="1"/>
-    <col min="30" max="31" width="44.54296875" style="1" customWidth="1"/>
-    <col min="32" max="33" width="18.453125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="11.140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.5703125" style="2" customWidth="1"/>
+    <col min="27" max="28" width="9.42578125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="20.42578125" style="2" customWidth="1"/>
+    <col min="30" max="31" width="44.5703125" style="1" customWidth="1"/>
+    <col min="32" max="33" width="18.42578125" style="2" customWidth="1"/>
     <col min="34" max="36" width="19" style="2" customWidth="1"/>
-    <col min="37" max="37" width="8.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="15" style="1" customWidth="1"/>
-    <col min="41" max="41" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="17" style="1" customWidth="1"/>
-    <col min="44" max="44" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="6.54296875" style="2" customWidth="1"/>
-    <col min="48" max="48" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="6.54296875" style="2" customWidth="1"/>
-    <col min="50" max="50" width="10.453125" style="1" customWidth="1"/>
-    <col min="51" max="51" width="27.54296875" style="1" customWidth="1"/>
-    <col min="52" max="52" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="16384" width="8.81640625" style="1"/>
+    <col min="44" max="44" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="6.5703125" style="2" customWidth="1"/>
+    <col min="48" max="48" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="6.5703125" style="2" customWidth="1"/>
+    <col min="50" max="50" width="10.42578125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="27.5703125" style="1" customWidth="1"/>
+    <col min="52" max="52" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:51" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>974</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6177,7 +6177,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>2</v>
       </c>
@@ -6901,7 +6901,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="16" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>3</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>5</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="18" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>7</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>8</v>
       </c>
@@ -7726,7 +7726,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>8</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>8</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>8</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>8</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>8</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>8</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>8</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>8</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="29" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>9</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="30" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>9</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="31" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>9</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="32" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>10</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="33" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>10</v>
       </c>
@@ -9514,7 +9514,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>14</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>14</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>14</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>14</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>14</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>14</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>16</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>16</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>16</v>
       </c>
@@ -10799,7 +10799,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>17</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>2.4390243902439024</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>17</v>
       </c>
@@ -10963,7 +10963,7 @@
         <v>7.3170731707317076</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>17</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>7.3170731707317076</v>
       </c>
     </row>
-    <row r="46" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>17</v>
       </c>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="AW46" s="11"/>
     </row>
-    <row r="47" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>18</v>
       </c>
@@ -11267,7 +11267,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="48" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>18</v>
       </c>
@@ -11404,7 +11404,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>20</v>
       </c>
@@ -11546,7 +11546,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>20</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>20</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="52" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>20</v>
       </c>
@@ -11963,7 +11963,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>20</v>
       </c>
@@ -12102,7 +12102,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:50" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>20</v>
       </c>
@@ -12244,7 +12244,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>20</v>
       </c>
@@ -12383,7 +12383,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>20</v>
       </c>
@@ -12522,7 +12522,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>20</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="58" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>20</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="59" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>21</v>
       </c>
@@ -12945,7 +12945,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>21</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>22</v>
       </c>
@@ -13226,7 +13226,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>22</v>
       </c>
@@ -13363,7 +13363,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>22</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="64" spans="1:50" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>22</v>
       </c>
@@ -13636,7 +13636,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="65" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>22</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="66" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>22</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="67" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>22</v>
       </c>
@@ -14041,7 +14041,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="68" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>22</v>
       </c>
@@ -14176,7 +14176,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="69" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>22</v>
       </c>
@@ -14311,7 +14311,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="70" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>22</v>
       </c>
@@ -14449,7 +14449,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="71" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>23</v>
       </c>
@@ -14588,7 +14588,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="72" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>23</v>
       </c>
@@ -14730,7 +14730,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="73" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>25</v>
       </c>
@@ -14873,7 +14873,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="74" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>25</v>
       </c>
@@ -15016,7 +15016,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="75" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>25</v>
       </c>
@@ -15160,7 +15160,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="76" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:49" s="8" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>26</v>
       </c>
@@ -15297,7 +15297,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="77" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:49" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>27</v>
       </c>
@@ -15434,7 +15434,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="78" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>27</v>
       </c>
@@ -15571,7 +15571,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="79" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:49" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>27</v>
       </c>
@@ -15708,7 +15708,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="80" spans="1:49" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:49" s="22" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="22">
         <v>27</v>
       </c>
@@ -15848,7 +15848,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>27</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="82" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>27</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="83" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>27</v>
       </c>
@@ -16259,7 +16259,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="84" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>27</v>
       </c>
@@ -16399,7 +16399,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>28</v>
       </c>
@@ -16545,7 +16545,7 @@
         <v>8.3333333333333321</v>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>28</v>
       </c>
@@ -16691,7 +16691,7 @@
         <v>58.63636363636364</v>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>28</v>
       </c>
@@ -16837,7 +16837,7 @@
         <v>11.363636363636363</v>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>28</v>
       </c>
@@ -16984,7 +16984,7 @@
         <v>36.679536679536682</v>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>28</v>
       </c>
@@ -17131,7 +17131,7 @@
         <v>6.5512517125420446</v>
       </c>
     </row>
-    <row r="90" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>28</v>
       </c>
@@ -17277,7 +17277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>28</v>
       </c>
@@ -17424,7 +17424,7 @@
         <v>34.234234234234236</v>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>28</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>62.166891300749562</v>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>28</v>
       </c>
@@ -17718,7 +17718,7 @@
         <v>9.9099099099099011</v>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>28</v>
       </c>
@@ -17865,7 +17865,7 @@
         <v>23.273657289002564</v>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>28</v>
       </c>
@@ -18012,7 +18012,7 @@
         <v>71.803069053708441</v>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>28</v>
       </c>
@@ -18159,7 +18159,7 @@
         <v>42.455242966751925</v>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>28</v>
       </c>
@@ -18306,7 +18306,7 @@
         <v>28.169014084507033</v>
       </c>
     </row>
-    <row r="98" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>28</v>
       </c>
@@ -18453,7 +18453,7 @@
         <v>64.967989756722162</v>
       </c>
     </row>
-    <row r="99" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>28</v>
       </c>
@@ -18600,7 +18600,7 @@
         <v>7.0422535211267583</v>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>28</v>
       </c>
@@ -18747,7 +18747,7 @@
         <v>39.344262295081968</v>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>28</v>
       </c>
@@ -18894,7 +18894,7 @@
         <v>60.000000000000007</v>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>28</v>
       </c>
@@ -19041,7 +19041,7 @@
         <v>60.655737704918032</v>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>28</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>30.705394190871377</v>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>28</v>
       </c>
@@ -19335,7 +19335,7 @@
         <v>48.091286307053934</v>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>28</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>32.780082987551864</v>
       </c>
     </row>
-    <row r="106" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>28</v>
       </c>
@@ -19629,7 +19629,7 @@
         <v>-26.842105263157919</v>
       </c>
     </row>
-    <row r="107" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>28</v>
       </c>
@@ -19776,7 +19776,7 @@
         <v>-7.1889952153110155</v>
       </c>
     </row>
-    <row r="108" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:50" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>28</v>
       </c>
@@ -19925,7 +19925,7 @@
         <v>-46.842105263157904</v>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>29</v>
       </c>
@@ -20070,7 +20070,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>29</v>
       </c>
@@ -20215,7 +20215,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>29</v>
       </c>
@@ -20360,7 +20360,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="112" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>29</v>
       </c>
@@ -20505,7 +20505,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="113" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:51" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>29</v>
       </c>
@@ -20651,7 +20651,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="114" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:51" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>31</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="115" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>31</v>
       </c>
@@ -20929,7 +20929,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="116" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>31</v>
       </c>
@@ -21068,7 +21068,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="117" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>31</v>
       </c>
@@ -21207,7 +21207,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="118" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>31</v>
       </c>
@@ -21348,7 +21348,7 @@
       <c r="AX118" s="1"/>
       <c r="AY118" s="1"/>
     </row>
-    <row r="119" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>31</v>
       </c>
@@ -21489,7 +21489,7 @@
       <c r="AX119" s="8"/>
       <c r="AY119" s="8"/>
     </row>
-    <row r="120" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>32</v>
       </c>
@@ -21632,7 +21632,7 @@
       </c>
       <c r="AY120" s="1"/>
     </row>
-    <row r="121" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>32</v>
       </c>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="AY121" s="1"/>
     </row>
-    <row r="122" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>32</v>
       </c>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="AY122" s="1"/>
     </row>
-    <row r="123" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>32</v>
       </c>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="AY123" s="1"/>
     </row>
-    <row r="124" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>32</v>
       </c>
@@ -22202,7 +22202,7 @@
       <c r="AX124" s="1"/>
       <c r="AY124" s="1"/>
     </row>
-    <row r="125" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>32</v>
       </c>
@@ -22345,7 +22345,7 @@
       </c>
       <c r="AY125" s="1"/>
     </row>
-    <row r="126" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>32</v>
       </c>
@@ -22488,7 +22488,7 @@
       </c>
       <c r="AY126" s="1"/>
     </row>
-    <row r="127" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>32</v>
       </c>
@@ -22631,7 +22631,7 @@
       </c>
       <c r="AY127" s="1"/>
     </row>
-    <row r="128" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>32</v>
       </c>
@@ -22772,7 +22772,7 @@
       <c r="AX128" s="1"/>
       <c r="AY128" s="1"/>
     </row>
-    <row r="129" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>32</v>
       </c>
@@ -22913,7 +22913,7 @@
       <c r="AX129" s="1"/>
       <c r="AY129" s="1"/>
     </row>
-    <row r="130" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>32</v>
       </c>
@@ -23054,7 +23054,7 @@
       <c r="AX130" s="1"/>
       <c r="AY130" s="36"/>
     </row>
-    <row r="131" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>32</v>
       </c>
@@ -23195,7 +23195,7 @@
       <c r="AX131" s="1"/>
       <c r="AY131" s="36"/>
     </row>
-    <row r="132" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>32</v>
       </c>
@@ -23336,7 +23336,7 @@
       <c r="AX132" s="8"/>
       <c r="AY132" s="36"/>
     </row>
-    <row r="133" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>34</v>
       </c>
@@ -23485,7 +23485,7 @@
       <c r="AX133" s="1"/>
       <c r="AY133" s="3"/>
     </row>
-    <row r="134" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>34</v>
       </c>
@@ -23634,7 +23634,7 @@
       <c r="AX134" s="1"/>
       <c r="AY134" s="1"/>
     </row>
-    <row r="135" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>34</v>
       </c>
@@ -23784,7 +23784,7 @@
       <c r="AX135" s="1"/>
       <c r="AY135" s="1"/>
     </row>
-    <row r="136" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>34</v>
       </c>
@@ -23934,7 +23934,7 @@
       <c r="AX136" s="1"/>
       <c r="AY136" s="1"/>
     </row>
-    <row r="137" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>35</v>
       </c>
@@ -24075,7 +24075,7 @@
       <c r="AX137" s="1"/>
       <c r="AY137" s="1"/>
     </row>
-    <row r="138" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>35</v>
       </c>
@@ -24216,7 +24216,7 @@
       <c r="AX138" s="1"/>
       <c r="AY138" s="1"/>
     </row>
-    <row r="139" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>35</v>
       </c>
@@ -24357,7 +24357,7 @@
       <c r="AX139" s="1"/>
       <c r="AY139" s="1"/>
     </row>
-    <row r="140" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>35</v>
       </c>
@@ -24498,7 +24498,7 @@
       <c r="AX140" s="1"/>
       <c r="AY140" s="1"/>
     </row>
-    <row r="141" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>35</v>
       </c>
@@ -24639,7 +24639,7 @@
       <c r="AX141" s="1"/>
       <c r="AY141" s="1"/>
     </row>
-    <row r="142" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>35</v>
       </c>
@@ -24780,7 +24780,7 @@
       <c r="AX142" s="1"/>
       <c r="AY142" s="1"/>
     </row>
-    <row r="143" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>35</v>
       </c>
@@ -24921,7 +24921,7 @@
       <c r="AX143" s="1"/>
       <c r="AY143" s="1"/>
     </row>
-    <row r="144" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>35</v>
       </c>
@@ -25062,7 +25062,7 @@
       <c r="AX144" s="8"/>
       <c r="AY144" s="8"/>
     </row>
-    <row r="145" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>36</v>
       </c>
@@ -25203,7 +25203,7 @@
       <c r="AX145" s="36"/>
       <c r="AY145" s="1"/>
     </row>
-    <row r="146" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>36</v>
       </c>
@@ -25344,7 +25344,7 @@
       <c r="AX146" s="36"/>
       <c r="AY146" s="1"/>
     </row>
-    <row r="147" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>36</v>
       </c>
@@ -25485,7 +25485,7 @@
       <c r="AX147" s="36"/>
       <c r="AY147" s="1"/>
     </row>
-    <row r="148" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>36</v>
       </c>
@@ -25626,7 +25626,7 @@
       <c r="AX148" s="36"/>
       <c r="AY148" s="1"/>
     </row>
-    <row r="149" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>36</v>
       </c>
@@ -25767,7 +25767,7 @@
       <c r="AX149" s="36"/>
       <c r="AY149" s="1"/>
     </row>
-    <row r="150" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>36</v>
       </c>
@@ -25908,7 +25908,7 @@
       <c r="AX150" s="36"/>
       <c r="AY150" s="1"/>
     </row>
-    <row r="151" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>36</v>
       </c>
@@ -26049,7 +26049,7 @@
       <c r="AX151" s="36"/>
       <c r="AY151" s="1"/>
     </row>
-    <row r="152" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>36</v>
       </c>
@@ -26190,7 +26190,7 @@
       <c r="AX152" s="36"/>
       <c r="AY152" s="1"/>
     </row>
-    <row r="153" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>36</v>
       </c>
@@ -26331,7 +26331,7 @@
       <c r="AX153" s="36"/>
       <c r="AY153" s="1"/>
     </row>
-    <row r="154" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>36</v>
       </c>
@@ -26472,7 +26472,7 @@
       <c r="AX154" s="36"/>
       <c r="AY154" s="1"/>
     </row>
-    <row r="155" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>36</v>
       </c>
@@ -26613,7 +26613,7 @@
       <c r="AX155" s="36"/>
       <c r="AY155" s="1"/>
     </row>
-    <row r="156" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>36</v>
       </c>
@@ -26754,7 +26754,7 @@
       <c r="AX156" s="36"/>
       <c r="AY156" s="1"/>
     </row>
-    <row r="157" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>36</v>
       </c>
@@ -26895,7 +26895,7 @@
       <c r="AX157" s="36"/>
       <c r="AY157" s="1"/>
     </row>
-    <row r="158" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>36</v>
       </c>
@@ -27036,7 +27036,7 @@
       <c r="AX158" s="36"/>
       <c r="AY158" s="1"/>
     </row>
-    <row r="159" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>36</v>
       </c>
@@ -27177,7 +27177,7 @@
       <c r="AX159" s="36"/>
       <c r="AY159" s="1"/>
     </row>
-    <row r="160" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>36</v>
       </c>
@@ -27318,7 +27318,7 @@
       <c r="AX160" s="37"/>
       <c r="AY160" s="8"/>
     </row>
-    <row r="161" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>37</v>
       </c>
@@ -27458,7 +27458,7 @@
       <c r="AX161" s="1"/>
       <c r="AY161" s="1"/>
     </row>
-    <row r="162" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>38</v>
       </c>
@@ -27608,7 +27608,7 @@
       </c>
       <c r="AY162" s="1"/>
     </row>
-    <row r="163" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>38</v>
       </c>
@@ -27756,7 +27756,7 @@
       <c r="AX163" s="1"/>
       <c r="AY163" s="1"/>
     </row>
-    <row r="164" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>38</v>
       </c>
@@ -27904,7 +27904,7 @@
       <c r="AX164" s="1"/>
       <c r="AY164" s="1"/>
     </row>
-    <row r="165" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>38</v>
       </c>
@@ -28052,7 +28052,7 @@
       <c r="AX165" s="8"/>
       <c r="AY165" s="8"/>
     </row>
-    <row r="166" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>39</v>
       </c>
@@ -28195,7 +28195,7 @@
       </c>
       <c r="AY166" s="1"/>
     </row>
-    <row r="167" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>39</v>
       </c>
@@ -28336,7 +28336,7 @@
       <c r="AX167" s="1"/>
       <c r="AY167" s="1"/>
     </row>
-    <row r="168" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>39</v>
       </c>
@@ -28477,7 +28477,7 @@
       <c r="AX168" s="1"/>
       <c r="AY168" s="1"/>
     </row>
-    <row r="169" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>39</v>
       </c>
@@ -28618,7 +28618,7 @@
       <c r="AX169" s="1"/>
       <c r="AY169" s="1"/>
     </row>
-    <row r="170" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>39</v>
       </c>
@@ -28759,7 +28759,7 @@
       <c r="AX170" s="1"/>
       <c r="AY170" s="1"/>
     </row>
-    <row r="171" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>39</v>
       </c>
@@ -28900,7 +28900,7 @@
       <c r="AX171" s="1"/>
       <c r="AY171" s="1"/>
     </row>
-    <row r="172" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>39</v>
       </c>
@@ -29041,7 +29041,7 @@
       <c r="AX172" s="1"/>
       <c r="AY172" s="1"/>
     </row>
-    <row r="173" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>39</v>
       </c>
@@ -29182,7 +29182,7 @@
       <c r="AX173" s="8"/>
       <c r="AY173" s="8"/>
     </row>
-    <row r="174" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>40</v>
       </c>
@@ -29331,7 +29331,7 @@
       </c>
       <c r="AY174" s="8"/>
     </row>
-    <row r="175" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>41</v>
       </c>
@@ -29468,7 +29468,7 @@
       </c>
       <c r="AY175" s="1"/>
     </row>
-    <row r="176" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>41</v>
       </c>
@@ -29602,7 +29602,7 @@
       </c>
       <c r="AY176" s="1"/>
     </row>
-    <row r="177" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>41</v>
       </c>
@@ -29737,7 +29737,7 @@
       <c r="AX177" s="1"/>
       <c r="AY177" s="1"/>
     </row>
-    <row r="178" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>41</v>
       </c>
@@ -29872,7 +29872,7 @@
       <c r="AX178" s="1"/>
       <c r="AY178" s="1"/>
     </row>
-    <row r="179" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>41</v>
       </c>
@@ -30007,7 +30007,7 @@
       <c r="AX179" s="1"/>
       <c r="AY179" s="1"/>
     </row>
-    <row r="180" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>41</v>
       </c>
@@ -30142,7 +30142,7 @@
       <c r="AX180" s="1"/>
       <c r="AY180" s="1"/>
     </row>
-    <row r="181" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>41</v>
       </c>
@@ -30277,7 +30277,7 @@
       <c r="AX181" s="1"/>
       <c r="AY181" s="1"/>
     </row>
-    <row r="182" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>42</v>
       </c>
@@ -30424,7 +30424,7 @@
       </c>
       <c r="AY182" s="1"/>
     </row>
-    <row r="183" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>42</v>
       </c>
@@ -30569,7 +30569,7 @@
       <c r="AX183" s="8"/>
       <c r="AY183" s="8"/>
     </row>
-    <row r="184" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>43</v>
       </c>
@@ -30709,7 +30709,7 @@
       <c r="AX184" s="1"/>
       <c r="AY184" s="1"/>
     </row>
-    <row r="185" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>43</v>
       </c>
@@ -30849,7 +30849,7 @@
       <c r="AX185" s="1"/>
       <c r="AY185" s="1"/>
     </row>
-    <row r="186" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>43</v>
       </c>
@@ -30989,7 +30989,7 @@
       <c r="AX186" s="1"/>
       <c r="AY186" s="1"/>
     </row>
-    <row r="187" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>44</v>
       </c>
@@ -31129,7 +31129,7 @@
       <c r="AX187" s="1"/>
       <c r="AY187" s="1"/>
     </row>
-    <row r="188" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>44</v>
       </c>
@@ -31269,7 +31269,7 @@
       <c r="AX188" s="1"/>
       <c r="AY188" s="1"/>
     </row>
-    <row r="189" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>44</v>
       </c>
@@ -31409,7 +31409,7 @@
       <c r="AX189" s="1"/>
       <c r="AY189" s="1"/>
     </row>
-    <row r="190" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>44</v>
       </c>
@@ -31549,7 +31549,7 @@
       <c r="AX190" s="1"/>
       <c r="AY190" s="1"/>
     </row>
-    <row r="191" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>44</v>
       </c>
@@ -31690,7 +31690,7 @@
       <c r="AX191" s="1"/>
       <c r="AY191" s="1"/>
     </row>
-    <row r="192" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>44</v>
       </c>
@@ -31831,7 +31831,7 @@
       <c r="AX192" s="1"/>
       <c r="AY192" s="1"/>
     </row>
-    <row r="193" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>44</v>
       </c>
@@ -31972,7 +31972,7 @@
       <c r="AX193" s="1"/>
       <c r="AY193" s="1"/>
     </row>
-    <row r="194" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>45</v>
       </c>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="AY194" s="1"/>
     </row>
-    <row r="195" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>45</v>
       </c>
@@ -32256,7 +32256,7 @@
       <c r="AX195" s="1"/>
       <c r="AY195" s="1"/>
     </row>
-    <row r="196" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>45</v>
       </c>
@@ -32397,7 +32397,7 @@
       <c r="AX196" s="1"/>
       <c r="AY196" s="1"/>
     </row>
-    <row r="197" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>45</v>
       </c>
@@ -32538,7 +32538,7 @@
       <c r="AX197" s="1"/>
       <c r="AY197" s="1"/>
     </row>
-    <row r="198" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>45</v>
       </c>
@@ -32679,7 +32679,7 @@
       <c r="AX198" s="1"/>
       <c r="AY198" s="1"/>
     </row>
-    <row r="199" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>45</v>
       </c>
@@ -32820,7 +32820,7 @@
       <c r="AX199" s="1"/>
       <c r="AY199" s="1"/>
     </row>
-    <row r="200" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>45</v>
       </c>
@@ -32961,7 +32961,7 @@
       <c r="AX200" s="1"/>
       <c r="AY200" s="1"/>
     </row>
-    <row r="201" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>45</v>
       </c>
@@ -33102,7 +33102,7 @@
       <c r="AX201" s="1"/>
       <c r="AY201" s="1"/>
     </row>
-    <row r="202" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46</v>
       </c>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="AY202" s="8"/>
     </row>
-    <row r="203" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>46</v>
       </c>
@@ -33391,7 +33391,7 @@
       </c>
       <c r="AY203" s="1"/>
     </row>
-    <row r="204" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>46</v>
       </c>
@@ -33532,7 +33532,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="205" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>46</v>
       </c>
@@ -33671,7 +33671,7 @@
       <c r="AX205" s="1"/>
       <c r="AY205" s="3"/>
     </row>
-    <row r="206" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>46</v>
       </c>
@@ -33810,7 +33810,7 @@
       <c r="AX206" s="1"/>
       <c r="AY206" s="3"/>
     </row>
-    <row r="207" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>47</v>
       </c>
@@ -33951,7 +33951,7 @@
       <c r="AX207" s="1"/>
       <c r="AY207" s="1"/>
     </row>
-    <row r="208" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>47</v>
       </c>
@@ -34092,7 +34092,7 @@
       <c r="AX208" s="1"/>
       <c r="AY208" s="1"/>
     </row>
-    <row r="209" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="8">
         <v>47</v>
       </c>
@@ -34233,7 +34233,7 @@
       <c r="AX209" s="8"/>
       <c r="AY209" s="8"/>
     </row>
-    <row r="210" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>48</v>
       </c>
@@ -34382,7 +34382,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="211" spans="1:51" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:51" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="22">
         <v>48</v>
       </c>
@@ -34530,7 +34530,7 @@
       <c r="AX211" s="22"/>
       <c r="AY211" s="22"/>
     </row>
-    <row r="212" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>48</v>
       </c>
@@ -34677,7 +34677,7 @@
       <c r="AX212" s="1"/>
       <c r="AY212" s="1"/>
     </row>
-    <row r="213" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="8">
         <v>48</v>
       </c>
@@ -34826,7 +34826,7 @@
       </c>
       <c r="AY213" s="8"/>
     </row>
-    <row r="214" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>49</v>
       </c>
@@ -34975,7 +34975,7 @@
       <c r="AX214" s="1"/>
       <c r="AY214" s="1"/>
     </row>
-    <row r="215" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>49</v>
       </c>
@@ -35124,7 +35124,7 @@
       <c r="AX215" s="1"/>
       <c r="AY215" s="1"/>
     </row>
-    <row r="216" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>49</v>
       </c>
@@ -35273,7 +35273,7 @@
       <c r="AX216" s="8"/>
       <c r="AY216" s="8"/>
     </row>
-    <row r="217" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>50</v>
       </c>
@@ -35416,7 +35416,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="218" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>50</v>
       </c>
@@ -35557,7 +35557,7 @@
       <c r="AX218" s="1"/>
       <c r="AY218" s="1"/>
     </row>
-    <row r="219" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>50</v>
       </c>
@@ -35698,7 +35698,7 @@
       <c r="AX219" s="1"/>
       <c r="AY219" s="1"/>
     </row>
-    <row r="220" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>50</v>
       </c>
@@ -35840,7 +35840,7 @@
       <c r="AX220" s="1"/>
       <c r="AY220" s="1"/>
     </row>
-    <row r="221" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>50</v>
       </c>
@@ -35982,7 +35982,7 @@
       <c r="AX221" s="1"/>
       <c r="AY221" s="1"/>
     </row>
-    <row r="222" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>50</v>
       </c>
@@ -36124,7 +36124,7 @@
       <c r="AX222" s="1"/>
       <c r="AY222" s="1"/>
     </row>
-    <row r="223" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>50</v>
       </c>
@@ -36266,7 +36266,7 @@
       <c r="AX223" s="1"/>
       <c r="AY223" s="1"/>
     </row>
-    <row r="224" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>50</v>
       </c>
@@ -36408,7 +36408,7 @@
       <c r="AX224" s="1"/>
       <c r="AY224" s="1"/>
     </row>
-    <row r="225" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>51</v>
       </c>
@@ -36556,7 +36556,7 @@
       </c>
       <c r="AY225" s="1"/>
     </row>
-    <row r="226" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>51</v>
       </c>
@@ -36704,7 +36704,7 @@
       </c>
       <c r="AY226" s="1"/>
     </row>
-    <row r="227" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>51</v>
       </c>
@@ -36852,7 +36852,7 @@
       </c>
       <c r="AY227" s="1"/>
     </row>
-    <row r="228" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>51</v>
       </c>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="AY228" s="1"/>
     </row>
-    <row r="229" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>51</v>
       </c>
@@ -37148,7 +37148,7 @@
       </c>
       <c r="AY229" s="1"/>
     </row>
-    <row r="230" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>51</v>
       </c>
@@ -37297,7 +37297,7 @@
       </c>
       <c r="AY230" s="1"/>
     </row>
-    <row r="231" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>51</v>
       </c>
@@ -37447,7 +37447,7 @@
       </c>
       <c r="AY231" s="1"/>
     </row>
-    <row r="232" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>51</v>
       </c>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="AY232" s="1"/>
     </row>
-    <row r="233" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>51</v>
       </c>
@@ -37747,7 +37747,7 @@
       </c>
       <c r="AY233" s="1"/>
     </row>
-    <row r="234" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>51</v>
       </c>
@@ -37898,7 +37898,7 @@
       </c>
       <c r="AY234" s="1"/>
     </row>
-    <row r="235" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>51</v>
       </c>
@@ -38049,7 +38049,7 @@
       </c>
       <c r="AY235" s="1"/>
     </row>
-    <row r="236" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>51</v>
       </c>
@@ -38200,7 +38200,7 @@
       </c>
       <c r="AY236" s="1"/>
     </row>
-    <row r="237" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>51</v>
       </c>
@@ -38349,7 +38349,7 @@
       </c>
       <c r="AY237" s="1"/>
     </row>
-    <row r="238" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>51</v>
       </c>
@@ -38498,7 +38498,7 @@
       </c>
       <c r="AY238" s="1"/>
     </row>
-    <row r="239" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>51</v>
       </c>
@@ -38647,7 +38647,7 @@
       </c>
       <c r="AY239" s="1"/>
     </row>
-    <row r="240" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>51</v>
       </c>
@@ -38796,7 +38796,7 @@
       </c>
       <c r="AY240" s="1"/>
     </row>
-    <row r="241" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>51</v>
       </c>
@@ -38945,7 +38945,7 @@
       </c>
       <c r="AY241" s="1"/>
     </row>
-    <row r="242" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>51</v>
       </c>
@@ -39094,7 +39094,7 @@
       </c>
       <c r="AY242" s="1"/>
     </row>
-    <row r="243" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>51</v>
       </c>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="AY243" s="1"/>
     </row>
-    <row r="244" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>51</v>
       </c>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="AY244" s="1"/>
     </row>
-    <row r="245" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>51</v>
       </c>
@@ -39543,7 +39543,7 @@
       </c>
       <c r="AY245" s="1"/>
     </row>
-    <row r="246" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>51</v>
       </c>
@@ -39692,7 +39692,7 @@
       </c>
       <c r="AY246" s="1"/>
     </row>
-    <row r="247" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>51</v>
       </c>
@@ -39842,7 +39842,7 @@
       </c>
       <c r="AY247" s="1"/>
     </row>
-    <row r="248" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>51</v>
       </c>
@@ -39992,7 +39992,7 @@
       </c>
       <c r="AY248" s="1"/>
     </row>
-    <row r="249" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>51</v>
       </c>
@@ -40140,7 +40140,7 @@
       </c>
       <c r="AY249" s="1"/>
     </row>
-    <row r="250" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>51</v>
       </c>
@@ -40289,7 +40289,7 @@
       </c>
       <c r="AY250" s="1"/>
     </row>
-    <row r="251" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>51</v>
       </c>
@@ -40437,7 +40437,7 @@
       </c>
       <c r="AY251" s="1"/>
     </row>
-    <row r="252" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>51</v>
       </c>
@@ -40586,7 +40586,7 @@
       </c>
       <c r="AY252" s="1"/>
     </row>
-    <row r="253" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>51</v>
       </c>
@@ -40735,7 +40735,7 @@
       </c>
       <c r="AY253" s="1"/>
     </row>
-    <row r="254" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>51</v>
       </c>
@@ -40885,7 +40885,7 @@
       </c>
       <c r="AY254" s="1"/>
     </row>
-    <row r="255" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>51</v>
       </c>
@@ -41034,7 +41034,7 @@
       </c>
       <c r="AY255" s="1"/>
     </row>
-    <row r="256" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>51</v>
       </c>
@@ -41184,7 +41184,7 @@
       </c>
       <c r="AY256" s="1"/>
     </row>
-    <row r="257" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>51</v>
       </c>
@@ -41334,7 +41334,7 @@
       </c>
       <c r="AY257" s="1"/>
     </row>
-    <row r="258" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>51</v>
       </c>
@@ -41485,7 +41485,7 @@
       </c>
       <c r="AY258" s="1"/>
     </row>
-    <row r="259" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>51</v>
       </c>
@@ -41635,7 +41635,7 @@
       </c>
       <c r="AY259" s="1"/>
     </row>
-    <row r="260" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>51</v>
       </c>
@@ -41786,7 +41786,7 @@
       </c>
       <c r="AY260" s="1"/>
     </row>
-    <row r="261" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>51</v>
       </c>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="AY261" s="1"/>
     </row>
-    <row r="262" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>51</v>
       </c>
@@ -42088,7 +42088,7 @@
       </c>
       <c r="AY262" s="1"/>
     </row>
-    <row r="263" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>51</v>
       </c>
@@ -42239,7 +42239,7 @@
       </c>
       <c r="AY263" s="1"/>
     </row>
-    <row r="264" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>51</v>
       </c>
@@ -42390,7 +42390,7 @@
       </c>
       <c r="AY264" s="1"/>
     </row>
-    <row r="265" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>51</v>
       </c>
@@ -42541,7 +42541,7 @@
       </c>
       <c r="AY265" s="1"/>
     </row>
-    <row r="266" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>51</v>
       </c>
@@ -42691,7 +42691,7 @@
       </c>
       <c r="AY266" s="1"/>
     </row>
-    <row r="267" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>51</v>
       </c>
@@ -42841,7 +42841,7 @@
       </c>
       <c r="AY267" s="1"/>
     </row>
-    <row r="268" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>51</v>
       </c>
@@ -42992,7 +42992,7 @@
       </c>
       <c r="AY268" s="1"/>
     </row>
-    <row r="269" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="8">
         <v>51</v>
       </c>
@@ -43143,7 +43143,7 @@
       </c>
       <c r="AY269" s="8"/>
     </row>
-    <row r="270" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>55</v>
       </c>
@@ -43281,7 +43281,7 @@
       <c r="AX270" s="1"/>
       <c r="AY270" s="1"/>
     </row>
-    <row r="271" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:51" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="8">
         <v>55</v>
       </c>
@@ -43419,7 +43419,7 @@
       <c r="AX271" s="8"/>
       <c r="AY271" s="8"/>
     </row>
-    <row r="272" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>56</v>
       </c>
@@ -43564,7 +43564,7 @@
       <c r="AX272" s="1"/>
       <c r="AY272" s="1"/>
     </row>
-    <row r="273" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>56</v>
       </c>
@@ -43708,7 +43708,7 @@
       <c r="AX273" s="1"/>
       <c r="AY273" s="1"/>
     </row>
-    <row r="274" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>57</v>
       </c>
@@ -43813,7 +43813,7 @@
       <c r="AX274" s="1"/>
       <c r="AY274" s="1"/>
     </row>
-    <row r="275" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>57</v>
       </c>
@@ -43918,7 +43918,7 @@
       <c r="AX275" s="1"/>
       <c r="AY275" s="1"/>
     </row>
-    <row r="276" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>57</v>
       </c>
@@ -44023,7 +44023,7 @@
       <c r="AX276" s="1"/>
       <c r="AY276" s="1"/>
     </row>
-    <row r="277" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>57</v>
       </c>
@@ -44123,7 +44123,7 @@
       <c r="AX277" s="1"/>
       <c r="AY277" s="1"/>
     </row>
-    <row r="278" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>57</v>
       </c>
@@ -44223,7 +44223,7 @@
       <c r="AX278" s="1"/>
       <c r="AY278" s="1"/>
     </row>
-    <row r="279" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>57</v>
       </c>
@@ -44323,7 +44323,7 @@
       <c r="AX279" s="1"/>
       <c r="AY279" s="1"/>
     </row>
-    <row r="280" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>58</v>
       </c>
@@ -44429,7 +44429,7 @@
       <c r="AX280" s="1"/>
       <c r="AY280" s="1"/>
     </row>
-    <row r="281" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>58</v>
       </c>
@@ -44536,7 +44536,7 @@
       <c r="AX281" s="1"/>
       <c r="AY281" s="1"/>
     </row>
-    <row r="282" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:51" s="2" customFormat="1" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>58</v>
       </c>
@@ -44642,7 +44642,7 @@
       <c r="AX282" s="1"/>
       <c r="AY282" s="1"/>
     </row>
-    <row r="283" spans="1:51" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:51" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>58</v>
       </c>
@@ -44754,7 +44754,7 @@
       </c>
       <c r="AV283"/>
     </row>
-    <row r="284" spans="1:51" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>58</v>
       </c>
@@ -44864,7 +44864,7 @@
       </c>
       <c r="AV284"/>
     </row>
-    <row r="285" spans="1:51" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>58</v>
       </c>
@@ -44974,7 +44974,7 @@
       </c>
       <c r="AV285"/>
     </row>
-    <row r="286" spans="1:51" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>58</v>
       </c>
@@ -45084,7 +45084,7 @@
       </c>
       <c r="AV286"/>
     </row>
-    <row r="287" spans="1:51" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>58</v>
       </c>
@@ -45194,7 +45194,7 @@
       </c>
       <c r="AV287"/>
     </row>
-    <row r="288" spans="1:51" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:51" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>58</v>
       </c>
@@ -45303,7 +45303,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="289" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>58</v>
       </c>
@@ -45412,7 +45412,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="290" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>58</v>
       </c>
@@ -45521,7 +45521,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="291" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>58</v>
       </c>
@@ -45630,7 +45630,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="292" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>58</v>
       </c>
@@ -45739,7 +45739,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="293" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>58</v>
       </c>
@@ -45848,7 +45848,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="294" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>59</v>
       </c>
@@ -45929,7 +45929,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="295" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>59</v>
       </c>
@@ -46010,7 +46010,7 @@
         <v>76.400000000000006</v>
       </c>
     </row>
-    <row r="296" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>59</v>
       </c>
@@ -46091,7 +46091,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="297" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>59</v>
       </c>
@@ -46172,7 +46172,7 @@
         <v>66.099999999999994</v>
       </c>
     </row>
-    <row r="298" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>59</v>
       </c>
@@ -46253,7 +46253,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="299" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>59</v>
       </c>
@@ -46334,7 +46334,7 @@
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="300" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>59</v>
       </c>
@@ -46415,7 +46415,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="301" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>59</v>
       </c>
@@ -46496,7 +46496,7 @@
         <v>83.1</v>
       </c>
     </row>
-    <row r="302" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>59</v>
       </c>
@@ -46577,7 +46577,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="303" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>59</v>
       </c>
@@ -46658,7 +46658,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="304" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>59</v>
       </c>
@@ -46739,7 +46739,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="305" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>59</v>
       </c>
@@ -46820,7 +46820,7 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="306" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>59</v>
       </c>
@@ -46901,7 +46901,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="307" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>59</v>
       </c>
@@ -46982,7 +46982,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="308" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>59</v>
       </c>
@@ -47063,7 +47063,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="309" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>59</v>
       </c>
@@ -47144,7 +47144,7 @@
         <v>77.2</v>
       </c>
     </row>
-    <row r="310" spans="1:47" ht="73.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:47" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>60</v>
       </c>
@@ -47247,7 +47247,7 @@
         <v>67.34693877551021</v>
       </c>
     </row>
-    <row r="311" spans="1:47" ht="145.5" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:47" ht="150.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>61</v>
       </c>
@@ -47358,7 +47358,7 @@
         <v>85.294117647058826</v>
       </c>
     </row>
-    <row r="312" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>61</v>
       </c>
@@ -47463,7 +47463,7 @@
         <v>20.588235294117649</v>
       </c>
     </row>
-    <row r="313" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>61</v>
       </c>
@@ -47574,7 +47574,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="314" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>61</v>
       </c>
@@ -47679,7 +47679,7 @@
         <v>30.76923076923077</v>
       </c>
     </row>
-    <row r="315" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>61</v>
       </c>
@@ -47790,7 +47790,7 @@
         <v>84.269662921348313</v>
       </c>
     </row>
-    <row r="316" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>61</v>
       </c>
@@ -47895,7 +47895,7 @@
         <v>10.1123595505618</v>
       </c>
     </row>
-    <row r="317" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>61</v>
       </c>
@@ -48004,7 +48004,7 @@
         <v>-11.034482758620699</v>
       </c>
     </row>
-    <row r="318" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>61</v>
       </c>
@@ -48113,7 +48113,7 @@
         <v>18.96551724137931</v>
       </c>
     </row>
-    <row r="319" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>61</v>
       </c>
@@ -48218,7 +48218,7 @@
         <v>2.631578947368427</v>
       </c>
     </row>
-    <row r="320" spans="1:47" ht="145" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:47" ht="150" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>61</v>
       </c>
@@ -48323,7 +48323,7 @@
         <v>35.96491228070176</v>
       </c>
     </row>
-    <row r="321" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>62</v>
       </c>
@@ -48358,7 +48358,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="322" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>62</v>
       </c>
@@ -48393,7 +48393,7 @@
         <v>61.989795918367349</v>
       </c>
     </row>
-    <row r="323" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>62</v>
       </c>
@@ -48428,7 +48428,7 @@
         <v>38.676844783715005</v>
       </c>
     </row>
-    <row r="324" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>62</v>
       </c>
@@ -48463,7 +48463,7 @@
         <v>52.89473684210526</v>
       </c>
     </row>
-    <row r="325" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>62</v>
       </c>
@@ -48498,7 +48498,7 @@
         <v>31.607629427792915</v>
       </c>
     </row>
-    <row r="326" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>62</v>
       </c>
@@ -48533,7 +48533,7 @@
         <v>44.705882352941174</v>
       </c>
     </row>
-    <row r="327" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>62</v>
       </c>
@@ -48568,7 +48568,7 @@
         <v>37.16577540106951</v>
       </c>
     </row>
-    <row r="328" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>62</v>
       </c>
@@ -48603,7 +48603,7 @@
         <v>26.854219948849099</v>
       </c>
     </row>
-    <row r="329" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>62</v>
       </c>
@@ -48638,7 +48638,7 @@
         <v>35.038363171355499</v>
       </c>
     </row>
-    <row r="330" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>62</v>
       </c>
@@ -48673,7 +48673,7 @@
         <v>38.650306748466257</v>
       </c>
     </row>
-    <row r="331" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>62</v>
       </c>
@@ -48708,7 +48708,7 @@
         <v>64.916467780429585</v>
       </c>
     </row>
-    <row r="332" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:51" ht="75" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>62</v>
       </c>
@@ -48743,7 +48743,7 @@
         <v>67.910447761194035</v>
       </c>
     </row>
-    <row r="333" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:51" ht="90" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>63</v>
       </c>
@@ -48775,7 +48775,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="334" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:51" ht="90" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>63</v>
       </c>
@@ -48801,7 +48801,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="335" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:51" ht="90" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>63</v>
       </c>
@@ -48827,7 +48827,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="336" spans="1:51" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:51" ht="90" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>63</v>
       </c>
